--- a/artfynd/A 23629-2025 artfynd.xlsx
+++ b/artfynd/A 23629-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY49"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125428419</v>
+        <v>125434400</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577910</v>
+        <v>578115</v>
       </c>
       <c r="R2" t="n">
-        <v>7084203</v>
+        <v>7083983</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -769,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125428351</v>
+        <v>125428425</v>
       </c>
       <c r="B3" t="n">
-        <v>79428</v>
+        <v>91172</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578034</v>
+        <v>577972</v>
       </c>
       <c r="R3" t="n">
-        <v>7084012</v>
+        <v>7084172</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -883,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125434417</v>
+        <v>125434401</v>
       </c>
       <c r="B4" t="n">
-        <v>56714</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,42 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578143</v>
+        <v>578107</v>
       </c>
       <c r="R4" t="n">
-        <v>7083969</v>
+        <v>7083998</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -993,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125428394</v>
+        <v>125428432</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>92293</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,42 +993,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578110</v>
+        <v>577962</v>
       </c>
       <c r="R5" t="n">
-        <v>7083998</v>
+        <v>7084183</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1099,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125428353</v>
+        <v>125428378</v>
       </c>
       <c r="B6" t="n">
-        <v>79428</v>
+        <v>91457</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578140</v>
+        <v>577940</v>
       </c>
       <c r="R6" t="n">
-        <v>7083952</v>
+        <v>7084148</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1201,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125428430</v>
+        <v>125428388</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1241,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577976</v>
+        <v>578113</v>
       </c>
       <c r="R7" t="n">
-        <v>7084168</v>
+        <v>7083974</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1303,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125428361</v>
+        <v>125428413</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1315,38 +1299,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578081</v>
+        <v>578145</v>
       </c>
       <c r="R8" t="n">
-        <v>7084034</v>
+        <v>7083986</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1405,10 +1393,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125434400</v>
+        <v>125428350</v>
       </c>
       <c r="B9" t="n">
-        <v>79891</v>
+        <v>90977</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1417,25 +1405,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1445,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578115</v>
+        <v>577904</v>
       </c>
       <c r="R9" t="n">
-        <v>7083983</v>
+        <v>7084198</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1495,22 +1483,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125434416</v>
+        <v>125428387</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1519,42 +1507,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578014</v>
+        <v>578115</v>
       </c>
       <c r="R10" t="n">
-        <v>7084101</v>
+        <v>7084013</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1601,22 +1585,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125428425</v>
+        <v>125428430</v>
       </c>
       <c r="B11" t="n">
-        <v>91172</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1625,25 +1609,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1637,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577972</v>
+        <v>577976</v>
       </c>
       <c r="R11" t="n">
-        <v>7084172</v>
+        <v>7084168</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1715,10 +1699,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125428432</v>
+        <v>125434417</v>
       </c>
       <c r="B12" t="n">
-        <v>92293</v>
+        <v>56714</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1727,38 +1711,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577962</v>
+        <v>578143</v>
       </c>
       <c r="R12" t="n">
-        <v>7084183</v>
+        <v>7083969</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1805,19 +1797,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125428388</v>
+        <v>125428390</v>
       </c>
       <c r="B13" t="n">
         <v>79891</v>
@@ -1857,10 +1849,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578113</v>
+        <v>577905</v>
       </c>
       <c r="R13" t="n">
-        <v>7083974</v>
+        <v>7084216</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1919,10 +1911,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125428350</v>
+        <v>125428351</v>
       </c>
       <c r="B14" t="n">
-        <v>90977</v>
+        <v>79428</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1931,25 +1923,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,10 +1951,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577904</v>
+        <v>578034</v>
       </c>
       <c r="R14" t="n">
-        <v>7084198</v>
+        <v>7084012</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2021,10 +2013,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125428362</v>
+        <v>125434402</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2037,21 +2029,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2053,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>578083</v>
+        <v>578098</v>
       </c>
       <c r="R15" t="n">
-        <v>7084025</v>
+        <v>7084009</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2111,22 +2103,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125428366</v>
+        <v>125434403</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2139,39 +2131,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578079</v>
+        <v>577951</v>
       </c>
       <c r="R16" t="n">
-        <v>7084109</v>
+        <v>7084215</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2206,11 +2193,6 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2223,22 +2205,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125428374</v>
+        <v>125428414</v>
       </c>
       <c r="B17" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2247,31 +2229,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2280,10 +2261,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>578083</v>
+        <v>578131</v>
       </c>
       <c r="R17" t="n">
-        <v>7084025</v>
+        <v>7083979</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2342,10 +2323,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125434419</v>
+        <v>125428415</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2354,38 +2335,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577944</v>
+        <v>578013</v>
       </c>
       <c r="R18" t="n">
-        <v>7084218</v>
+        <v>7084064</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2432,22 +2417,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125428368</v>
+        <v>125428394</v>
       </c>
       <c r="B19" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2456,38 +2441,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>577905</v>
+        <v>578110</v>
       </c>
       <c r="R19" t="n">
-        <v>7084216</v>
+        <v>7083998</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2546,10 +2535,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125428387</v>
+        <v>125428416</v>
       </c>
       <c r="B20" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2558,38 +2547,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>578115</v>
+        <v>577966</v>
       </c>
       <c r="R20" t="n">
-        <v>7084013</v>
+        <v>7084168</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2648,10 +2641,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125428379</v>
+        <v>125428411</v>
       </c>
       <c r="B21" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2660,38 +2653,42 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>578081</v>
+        <v>578021</v>
       </c>
       <c r="R21" t="n">
-        <v>7084034</v>
+        <v>7084086</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2750,10 +2747,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125434401</v>
+        <v>125428368</v>
       </c>
       <c r="B22" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2762,25 +2759,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2790,10 +2787,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>578107</v>
+        <v>577905</v>
       </c>
       <c r="R22" t="n">
-        <v>7083998</v>
+        <v>7084216</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2840,19 +2837,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125434414</v>
+        <v>125428408</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -2887,7 +2884,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2896,10 +2893,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>578153</v>
+        <v>577986</v>
       </c>
       <c r="R23" t="n">
-        <v>7083956</v>
+        <v>7084157</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2946,22 +2943,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125434403</v>
+        <v>125428361</v>
       </c>
       <c r="B24" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2974,21 +2971,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2998,10 +2995,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>577951</v>
+        <v>578081</v>
       </c>
       <c r="R24" t="n">
-        <v>7084215</v>
+        <v>7084034</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3048,19 +3045,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125428412</v>
+        <v>125428417</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3095,7 +3092,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3104,10 +3101,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>578120</v>
+        <v>577924</v>
       </c>
       <c r="R25" t="n">
-        <v>7084012</v>
+        <v>7084207</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3166,10 +3163,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125428416</v>
+        <v>125428362</v>
       </c>
       <c r="B26" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3178,42 +3175,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577966</v>
+        <v>578083</v>
       </c>
       <c r="R26" t="n">
-        <v>7084168</v>
+        <v>7084025</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3272,10 +3265,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125428397</v>
+        <v>125434419</v>
       </c>
       <c r="B27" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3288,21 +3281,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3312,10 +3305,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>578084</v>
+        <v>577944</v>
       </c>
       <c r="R27" t="n">
-        <v>7084110</v>
+        <v>7084218</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3362,22 +3355,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125428376</v>
+        <v>125428399</v>
       </c>
       <c r="B28" t="n">
-        <v>57529</v>
+        <v>78546</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3390,39 +3383,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577907</v>
+        <v>577919</v>
       </c>
       <c r="R28" t="n">
-        <v>7084187</v>
+        <v>7084186</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3481,10 +3469,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125428363</v>
+        <v>125428392</v>
       </c>
       <c r="B29" t="n">
-        <v>91012</v>
+        <v>79927</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3493,25 +3481,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3521,10 +3509,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>578090</v>
+        <v>577919</v>
       </c>
       <c r="R29" t="n">
-        <v>7084017</v>
+        <v>7084203</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3583,10 +3571,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125434404</v>
+        <v>125428367</v>
       </c>
       <c r="B30" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3599,34 +3587,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577934</v>
+        <v>578014</v>
       </c>
       <c r="R30" t="n">
-        <v>7084194</v>
+        <v>7084091</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3661,6 +3654,11 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3673,22 +3671,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125428377</v>
+        <v>125428363</v>
       </c>
       <c r="B31" t="n">
-        <v>91457</v>
+        <v>91012</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3697,25 +3695,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3725,7 +3723,7 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>578093</v>
+        <v>578090</v>
       </c>
       <c r="R31" t="n">
         <v>7084017</v>
@@ -3787,10 +3785,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125434405</v>
+        <v>125434416</v>
       </c>
       <c r="B32" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3799,38 +3797,42 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577902</v>
+        <v>578014</v>
       </c>
       <c r="R32" t="n">
-        <v>7084214</v>
+        <v>7084101</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3889,10 +3891,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125428389</v>
+        <v>125434413</v>
       </c>
       <c r="B33" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3901,38 +3903,42 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>577934</v>
+        <v>578042</v>
       </c>
       <c r="R33" t="n">
-        <v>7084181</v>
+        <v>7084048</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3979,22 +3985,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125428408</v>
+        <v>125428404</v>
       </c>
       <c r="B34" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4003,42 +4009,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577986</v>
+        <v>578140</v>
       </c>
       <c r="R34" t="n">
-        <v>7084157</v>
+        <v>7083952</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4097,10 +4099,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125428415</v>
+        <v>125428366</v>
       </c>
       <c r="B35" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4109,30 +4111,31 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4141,10 +4144,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578013</v>
+        <v>578079</v>
       </c>
       <c r="R35" t="n">
-        <v>7084064</v>
+        <v>7084109</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4177,6 +4180,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4203,10 +4211,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125428411</v>
+        <v>125428377</v>
       </c>
       <c r="B36" t="n">
-        <v>98101</v>
+        <v>91457</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4219,38 +4227,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>578021</v>
+        <v>578093</v>
       </c>
       <c r="R36" t="n">
-        <v>7084086</v>
+        <v>7084017</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4309,10 +4313,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125428375</v>
+        <v>125428389</v>
       </c>
       <c r="B37" t="n">
-        <v>57529</v>
+        <v>79891</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4325,39 +4329,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>578148</v>
+        <v>577934</v>
       </c>
       <c r="R37" t="n">
-        <v>7083982</v>
+        <v>7084181</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4416,10 +4415,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125428378</v>
+        <v>125428364</v>
       </c>
       <c r="B38" t="n">
-        <v>91457</v>
+        <v>91012</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4428,25 +4427,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4456,10 +4455,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577940</v>
+        <v>577941</v>
       </c>
       <c r="R38" t="n">
-        <v>7084148</v>
+        <v>7084160</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4518,10 +4517,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125428428</v>
+        <v>125428376</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4534,34 +4533,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>578052</v>
+        <v>577907</v>
       </c>
       <c r="R39" t="n">
-        <v>7084030</v>
+        <v>7084187</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4620,10 +4624,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125434402</v>
+        <v>125434414</v>
       </c>
       <c r="B40" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4632,38 +4636,42 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>578098</v>
+        <v>578153</v>
       </c>
       <c r="R40" t="n">
-        <v>7084009</v>
+        <v>7083956</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4722,7 +4730,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125428390</v>
+        <v>125434404</v>
       </c>
       <c r="B41" t="n">
         <v>79891</v>
@@ -4762,10 +4770,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577905</v>
+        <v>577934</v>
       </c>
       <c r="R41" t="n">
-        <v>7084216</v>
+        <v>7084194</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4812,19 +4820,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125428399</v>
+        <v>125428397</v>
       </c>
       <c r="B42" t="n">
         <v>78546</v>
@@ -4864,10 +4872,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>577919</v>
+        <v>578084</v>
       </c>
       <c r="R42" t="n">
-        <v>7084186</v>
+        <v>7084110</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4926,10 +4934,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125428364</v>
+        <v>125428412</v>
       </c>
       <c r="B43" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4938,38 +4946,42 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>577941</v>
+        <v>578120</v>
       </c>
       <c r="R43" t="n">
-        <v>7084160</v>
+        <v>7084012</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5028,10 +5040,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125428392</v>
+        <v>125428419</v>
       </c>
       <c r="B44" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5040,35 +5052,39 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>577919</v>
+        <v>577910</v>
       </c>
       <c r="R44" t="n">
         <v>7084203</v>
@@ -5130,10 +5146,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125428417</v>
+        <v>125428428</v>
       </c>
       <c r="B45" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5142,42 +5158,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>577924</v>
+        <v>578052</v>
       </c>
       <c r="R45" t="n">
-        <v>7084207</v>
+        <v>7084030</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5236,10 +5248,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125428414</v>
+        <v>125434405</v>
       </c>
       <c r="B46" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5248,42 +5260,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>578131</v>
+        <v>577902</v>
       </c>
       <c r="R46" t="n">
-        <v>7083979</v>
+        <v>7084214</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5330,22 +5338,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125434413</v>
+        <v>125428379</v>
       </c>
       <c r="B47" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5354,42 +5362,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>578042</v>
+        <v>578081</v>
       </c>
       <c r="R47" t="n">
-        <v>7084048</v>
+        <v>7084034</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5436,22 +5440,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125428367</v>
+        <v>125428374</v>
       </c>
       <c r="B48" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5464,16 +5468,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5493,10 +5497,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>578014</v>
+        <v>578083</v>
       </c>
       <c r="R48" t="n">
-        <v>7084091</v>
+        <v>7084025</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5529,11 +5533,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5560,10 +5559,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125428413</v>
+        <v>125428353</v>
       </c>
       <c r="B49" t="n">
-        <v>98101</v>
+        <v>79428</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5572,42 +5571,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>578145</v>
+        <v>578140</v>
       </c>
       <c r="R49" t="n">
-        <v>7083986</v>
+        <v>7083952</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5663,6 +5658,113 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>125428375</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Skirsjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>578148</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7083982</v>
+      </c>
+      <c r="S50" t="n">
+        <v>15</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23629-2025 artfynd.xlsx
+++ b/artfynd/A 23629-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125434400</v>
+        <v>125428416</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>98269</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578115</v>
+        <v>577966</v>
       </c>
       <c r="R2" t="n">
-        <v>7083983</v>
+        <v>7084168</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -765,22 +769,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125428425</v>
+        <v>125428413</v>
       </c>
       <c r="B3" t="n">
-        <v>91172</v>
+        <v>98269</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +797,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577972</v>
+        <v>578145</v>
       </c>
       <c r="R3" t="n">
-        <v>7084172</v>
+        <v>7083986</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125434401</v>
+        <v>125434419</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>78947</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578107</v>
+        <v>577944</v>
       </c>
       <c r="R4" t="n">
-        <v>7083998</v>
+        <v>7084218</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125428432</v>
+        <v>125428389</v>
       </c>
       <c r="B5" t="n">
-        <v>92293</v>
+        <v>80028</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +1001,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577962</v>
+        <v>577934</v>
       </c>
       <c r="R5" t="n">
-        <v>7084183</v>
+        <v>7084181</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125428378</v>
+        <v>125428376</v>
       </c>
       <c r="B6" t="n">
-        <v>91457</v>
+        <v>57632</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,38 +1103,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577940</v>
+        <v>577907</v>
       </c>
       <c r="R6" t="n">
-        <v>7084148</v>
+        <v>7084187</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,10 +1198,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125428388</v>
+        <v>125428378</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>91617</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1210,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1238,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578113</v>
+        <v>577940</v>
       </c>
       <c r="R7" t="n">
-        <v>7083974</v>
+        <v>7084148</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,10 +1300,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125428413</v>
+        <v>125428350</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>91131</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,42 +1312,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578145</v>
+        <v>577904</v>
       </c>
       <c r="R8" t="n">
-        <v>7083986</v>
+        <v>7084198</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1393,10 +1402,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125428350</v>
+        <v>125428361</v>
       </c>
       <c r="B9" t="n">
-        <v>90977</v>
+        <v>91166</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,25 +1414,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1442,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577904</v>
+        <v>578081</v>
       </c>
       <c r="R9" t="n">
-        <v>7084198</v>
+        <v>7084034</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1495,10 +1504,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125428387</v>
+        <v>125428432</v>
       </c>
       <c r="B10" t="n">
-        <v>79891</v>
+        <v>92448</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,25 +1516,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1535,10 +1544,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578115</v>
+        <v>577962</v>
       </c>
       <c r="R10" t="n">
-        <v>7084013</v>
+        <v>7084183</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1597,10 +1606,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125428430</v>
+        <v>125428404</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>78683</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1613,21 +1622,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1637,10 +1646,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577976</v>
+        <v>578140</v>
       </c>
       <c r="R11" t="n">
-        <v>7084168</v>
+        <v>7083952</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1699,10 +1708,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125434417</v>
+        <v>125428425</v>
       </c>
       <c r="B12" t="n">
-        <v>56714</v>
+        <v>91326</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,46 +1720,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>1503</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578143</v>
+        <v>577972</v>
       </c>
       <c r="R12" t="n">
-        <v>7083969</v>
+        <v>7084172</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1797,22 +1798,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125428390</v>
+        <v>125428397</v>
       </c>
       <c r="B13" t="n">
-        <v>79891</v>
+        <v>78683</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1825,21 +1826,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1849,10 +1850,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577905</v>
+        <v>578084</v>
       </c>
       <c r="R13" t="n">
-        <v>7084216</v>
+        <v>7084110</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1911,10 +1912,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125428351</v>
+        <v>125434405</v>
       </c>
       <c r="B14" t="n">
-        <v>79428</v>
+        <v>80028</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1927,21 +1928,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1951,10 +1952,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578034</v>
+        <v>577902</v>
       </c>
       <c r="R14" t="n">
-        <v>7084012</v>
+        <v>7084214</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2001,22 +2002,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125434402</v>
+        <v>125428374</v>
       </c>
       <c r="B15" t="n">
-        <v>79891</v>
+        <v>57632</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2029,34 +2030,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>578098</v>
+        <v>578083</v>
       </c>
       <c r="R15" t="n">
-        <v>7084009</v>
+        <v>7084025</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2103,22 +2109,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125434403</v>
+        <v>125428411</v>
       </c>
       <c r="B16" t="n">
-        <v>79891</v>
+        <v>98269</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2127,38 +2133,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577951</v>
+        <v>578021</v>
       </c>
       <c r="R16" t="n">
-        <v>7084215</v>
+        <v>7084086</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2205,22 +2215,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125428414</v>
+        <v>125434400</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>80028</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2229,42 +2239,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>578131</v>
+        <v>578115</v>
       </c>
       <c r="R17" t="n">
-        <v>7083979</v>
+        <v>7083983</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2311,22 +2317,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125428415</v>
+        <v>125428388</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>80028</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2335,42 +2341,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>578013</v>
+        <v>578113</v>
       </c>
       <c r="R18" t="n">
-        <v>7084064</v>
+        <v>7083974</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2429,10 +2431,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125428394</v>
+        <v>125428362</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>91166</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2441,42 +2443,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>578110</v>
+        <v>578083</v>
       </c>
       <c r="R19" t="n">
-        <v>7083998</v>
+        <v>7084025</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2535,10 +2533,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125428416</v>
+        <v>125428363</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>91166</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2547,42 +2545,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577966</v>
+        <v>578090</v>
       </c>
       <c r="R20" t="n">
-        <v>7084168</v>
+        <v>7084017</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2641,10 +2635,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125428411</v>
+        <v>125434417</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>56828</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2653,42 +2647,46 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>578021</v>
+        <v>578143</v>
       </c>
       <c r="R21" t="n">
-        <v>7084086</v>
+        <v>7083969</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2735,22 +2733,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125428368</v>
+        <v>125428394</v>
       </c>
       <c r="B22" t="n">
-        <v>79920</v>
+        <v>98269</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2759,38 +2757,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577905</v>
+        <v>578110</v>
       </c>
       <c r="R22" t="n">
-        <v>7084216</v>
+        <v>7083998</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2849,10 +2851,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125428408</v>
+        <v>125434413</v>
       </c>
       <c r="B23" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2884,7 +2886,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2893,10 +2895,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577986</v>
+        <v>578042</v>
       </c>
       <c r="R23" t="n">
-        <v>7084157</v>
+        <v>7084048</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2943,22 +2945,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125428361</v>
+        <v>125428412</v>
       </c>
       <c r="B24" t="n">
-        <v>91012</v>
+        <v>98269</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2967,38 +2969,42 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>578081</v>
+        <v>578120</v>
       </c>
       <c r="R24" t="n">
-        <v>7084034</v>
+        <v>7084012</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3057,10 +3063,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125428417</v>
+        <v>125428387</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>80028</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3069,42 +3075,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577924</v>
+        <v>578115</v>
       </c>
       <c r="R25" t="n">
-        <v>7084207</v>
+        <v>7084013</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3163,10 +3165,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125428362</v>
+        <v>125428392</v>
       </c>
       <c r="B26" t="n">
-        <v>91012</v>
+        <v>80064</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3175,25 +3177,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3203,10 +3205,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>578083</v>
+        <v>577919</v>
       </c>
       <c r="R26" t="n">
-        <v>7084025</v>
+        <v>7084203</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3265,10 +3267,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125434419</v>
+        <v>125434401</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>80028</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3281,21 +3283,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3305,10 +3307,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577944</v>
+        <v>578107</v>
       </c>
       <c r="R27" t="n">
-        <v>7084218</v>
+        <v>7083998</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3367,10 +3369,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125428399</v>
+        <v>125428351</v>
       </c>
       <c r="B28" t="n">
-        <v>78546</v>
+        <v>79565</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3383,21 +3385,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3407,10 +3409,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577919</v>
+        <v>578034</v>
       </c>
       <c r="R28" t="n">
-        <v>7084186</v>
+        <v>7084012</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3469,10 +3471,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125428392</v>
+        <v>125434403</v>
       </c>
       <c r="B29" t="n">
-        <v>79927</v>
+        <v>80028</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3481,25 +3483,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3509,10 +3511,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577919</v>
+        <v>577951</v>
       </c>
       <c r="R29" t="n">
-        <v>7084203</v>
+        <v>7084215</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3559,22 +3561,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125428367</v>
+        <v>125428364</v>
       </c>
       <c r="B30" t="n">
-        <v>57513</v>
+        <v>91166</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3587,39 +3589,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>578014</v>
+        <v>577941</v>
       </c>
       <c r="R30" t="n">
-        <v>7084091</v>
+        <v>7084160</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3652,11 +3649,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3683,10 +3675,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125428363</v>
+        <v>125428366</v>
       </c>
       <c r="B31" t="n">
-        <v>91012</v>
+        <v>57635</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3699,34 +3691,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>578090</v>
+        <v>578079</v>
       </c>
       <c r="R31" t="n">
-        <v>7084017</v>
+        <v>7084109</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3759,6 +3756,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3785,10 +3787,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125434416</v>
+        <v>125428428</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
+        <v>78947</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3797,42 +3799,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>578014</v>
+        <v>578052</v>
       </c>
       <c r="R32" t="n">
-        <v>7084101</v>
+        <v>7084030</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3879,22 +3877,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125434413</v>
+        <v>125434416</v>
       </c>
       <c r="B33" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3926,7 +3924,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3935,10 +3933,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>578042</v>
+        <v>578014</v>
       </c>
       <c r="R33" t="n">
-        <v>7084048</v>
+        <v>7084101</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3997,10 +3995,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125428404</v>
+        <v>125428377</v>
       </c>
       <c r="B34" t="n">
-        <v>78546</v>
+        <v>91617</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4009,25 +4007,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>1209</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4037,10 +4035,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>578140</v>
+        <v>578093</v>
       </c>
       <c r="R34" t="n">
-        <v>7083952</v>
+        <v>7084017</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4099,10 +4097,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125428366</v>
+        <v>125428379</v>
       </c>
       <c r="B35" t="n">
-        <v>57513</v>
+        <v>91459</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4115,39 +4113,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578079</v>
+        <v>578081</v>
       </c>
       <c r="R35" t="n">
-        <v>7084109</v>
+        <v>7084034</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4180,11 +4173,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4211,10 +4199,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125428377</v>
+        <v>125428417</v>
       </c>
       <c r="B36" t="n">
-        <v>91457</v>
+        <v>98269</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4227,34 +4215,38 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>578093</v>
+        <v>577924</v>
       </c>
       <c r="R36" t="n">
-        <v>7084017</v>
+        <v>7084207</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4313,10 +4305,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125428389</v>
+        <v>125428414</v>
       </c>
       <c r="B37" t="n">
-        <v>79891</v>
+        <v>98269</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4325,38 +4317,42 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>577934</v>
+        <v>578131</v>
       </c>
       <c r="R37" t="n">
-        <v>7084181</v>
+        <v>7083979</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4415,10 +4411,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125428364</v>
+        <v>125434414</v>
       </c>
       <c r="B38" t="n">
-        <v>91012</v>
+        <v>98269</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4427,38 +4423,42 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577941</v>
+        <v>578153</v>
       </c>
       <c r="R38" t="n">
-        <v>7084160</v>
+        <v>7083956</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4505,22 +4505,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125428376</v>
+        <v>125428390</v>
       </c>
       <c r="B39" t="n">
-        <v>57529</v>
+        <v>80028</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4533,39 +4533,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577907</v>
+        <v>577905</v>
       </c>
       <c r="R39" t="n">
-        <v>7084187</v>
+        <v>7084216</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4624,10 +4619,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125434414</v>
+        <v>125428368</v>
       </c>
       <c r="B40" t="n">
-        <v>98101</v>
+        <v>80057</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4636,42 +4631,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>578153</v>
+        <v>577905</v>
       </c>
       <c r="R40" t="n">
-        <v>7083956</v>
+        <v>7084216</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4718,22 +4709,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125434404</v>
+        <v>125428367</v>
       </c>
       <c r="B41" t="n">
-        <v>79891</v>
+        <v>57635</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4746,34 +4737,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577934</v>
+        <v>578014</v>
       </c>
       <c r="R41" t="n">
-        <v>7084194</v>
+        <v>7084091</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4808,6 +4804,11 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4820,22 +4821,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125428397</v>
+        <v>125428415</v>
       </c>
       <c r="B42" t="n">
-        <v>78546</v>
+        <v>98269</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4844,38 +4845,42 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>578084</v>
+        <v>578013</v>
       </c>
       <c r="R42" t="n">
-        <v>7084110</v>
+        <v>7084064</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4934,10 +4939,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125428412</v>
+        <v>125428408</v>
       </c>
       <c r="B43" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4969,7 +4974,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4978,10 +4983,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>578120</v>
+        <v>577986</v>
       </c>
       <c r="R43" t="n">
-        <v>7084012</v>
+        <v>7084157</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5040,10 +5045,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125428419</v>
+        <v>125434404</v>
       </c>
       <c r="B44" t="n">
-        <v>98101</v>
+        <v>80028</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5052,42 +5057,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>577910</v>
+        <v>577934</v>
       </c>
       <c r="R44" t="n">
-        <v>7084203</v>
+        <v>7084194</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5134,22 +5135,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125428428</v>
+        <v>125428399</v>
       </c>
       <c r="B45" t="n">
-        <v>78810</v>
+        <v>78683</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5162,21 +5163,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5186,10 +5187,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>578052</v>
+        <v>577919</v>
       </c>
       <c r="R45" t="n">
-        <v>7084030</v>
+        <v>7084186</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5248,10 +5249,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125434405</v>
+        <v>125434402</v>
       </c>
       <c r="B46" t="n">
-        <v>79891</v>
+        <v>80028</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5288,10 +5289,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>577902</v>
+        <v>578098</v>
       </c>
       <c r="R46" t="n">
-        <v>7084214</v>
+        <v>7084009</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5350,10 +5351,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125428379</v>
+        <v>125428430</v>
       </c>
       <c r="B47" t="n">
-        <v>91299</v>
+        <v>78947</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5366,21 +5367,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5390,10 +5391,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>578081</v>
+        <v>577976</v>
       </c>
       <c r="R47" t="n">
-        <v>7084034</v>
+        <v>7084168</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5452,10 +5453,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125428374</v>
+        <v>125428375</v>
       </c>
       <c r="B48" t="n">
-        <v>57529</v>
+        <v>57632</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5497,10 +5498,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>578083</v>
+        <v>578148</v>
       </c>
       <c r="R48" t="n">
-        <v>7084025</v>
+        <v>7083982</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5562,7 +5563,7 @@
         <v>125428353</v>
       </c>
       <c r="B49" t="n">
-        <v>79428</v>
+        <v>79565</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5661,10 +5662,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125428375</v>
+        <v>125428419</v>
       </c>
       <c r="B50" t="n">
-        <v>57529</v>
+        <v>98269</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5673,31 +5674,30 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5706,10 +5706,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>578148</v>
+        <v>577910</v>
       </c>
       <c r="R50" t="n">
-        <v>7083982</v>
+        <v>7084203</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>

--- a/artfynd/A 23629-2025 artfynd.xlsx
+++ b/artfynd/A 23629-2025 artfynd.xlsx
@@ -1606,10 +1606,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125428404</v>
+        <v>125428425</v>
       </c>
       <c r="B11" t="n">
-        <v>78683</v>
+        <v>91326</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1618,25 +1618,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578140</v>
+        <v>577972</v>
       </c>
       <c r="R11" t="n">
-        <v>7083952</v>
+        <v>7084172</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1708,10 +1708,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125428425</v>
+        <v>125428404</v>
       </c>
       <c r="B12" t="n">
-        <v>91326</v>
+        <v>78683</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1720,25 +1720,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1748,10 +1748,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577972</v>
+        <v>578140</v>
       </c>
       <c r="R12" t="n">
-        <v>7084172</v>
+        <v>7083952</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1810,10 +1810,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125428397</v>
+        <v>125428374</v>
       </c>
       <c r="B13" t="n">
-        <v>78683</v>
+        <v>57632</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1826,34 +1826,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578084</v>
+        <v>578083</v>
       </c>
       <c r="R13" t="n">
-        <v>7084110</v>
+        <v>7084025</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1912,10 +1917,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125434405</v>
+        <v>125428397</v>
       </c>
       <c r="B14" t="n">
-        <v>80028</v>
+        <v>78683</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1928,21 +1933,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1952,10 +1957,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577902</v>
+        <v>578084</v>
       </c>
       <c r="R14" t="n">
-        <v>7084214</v>
+        <v>7084110</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2002,22 +2007,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125428374</v>
+        <v>125434405</v>
       </c>
       <c r="B15" t="n">
-        <v>57632</v>
+        <v>80028</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2030,39 +2035,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>578083</v>
+        <v>577902</v>
       </c>
       <c r="R15" t="n">
-        <v>7084025</v>
+        <v>7084214</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2109,12 +2109,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2635,10 +2635,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125434417</v>
+        <v>125428387</v>
       </c>
       <c r="B21" t="n">
-        <v>56828</v>
+        <v>80028</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2651,42 +2651,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>578143</v>
+        <v>578115</v>
       </c>
       <c r="R21" t="n">
-        <v>7083969</v>
+        <v>7084013</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2733,22 +2725,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125428394</v>
+        <v>125428392</v>
       </c>
       <c r="B22" t="n">
-        <v>98269</v>
+        <v>80064</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2757,42 +2749,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>578110</v>
+        <v>577919</v>
       </c>
       <c r="R22" t="n">
-        <v>7083998</v>
+        <v>7084203</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2851,7 +2839,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125434413</v>
+        <v>125428394</v>
       </c>
       <c r="B23" t="n">
         <v>98269</v>
@@ -2886,7 +2874,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2895,10 +2883,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>578042</v>
+        <v>578110</v>
       </c>
       <c r="R23" t="n">
-        <v>7084048</v>
+        <v>7083998</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2945,19 +2933,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125428412</v>
+        <v>125434413</v>
       </c>
       <c r="B24" t="n">
         <v>98269</v>
@@ -3001,10 +2989,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>578120</v>
+        <v>578042</v>
       </c>
       <c r="R24" t="n">
-        <v>7084012</v>
+        <v>7084048</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3051,22 +3039,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125428387</v>
+        <v>125428412</v>
       </c>
       <c r="B25" t="n">
-        <v>80028</v>
+        <v>98269</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3075,38 +3063,42 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>578115</v>
+        <v>578120</v>
       </c>
       <c r="R25" t="n">
-        <v>7084013</v>
+        <v>7084012</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3165,10 +3157,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125428392</v>
+        <v>125434417</v>
       </c>
       <c r="B26" t="n">
-        <v>80064</v>
+        <v>56828</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3177,38 +3169,46 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6464</v>
+        <v>102612</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577919</v>
+        <v>578143</v>
       </c>
       <c r="R26" t="n">
-        <v>7084203</v>
+        <v>7083969</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3255,22 +3255,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125434401</v>
+        <v>125428366</v>
       </c>
       <c r="B27" t="n">
-        <v>80028</v>
+        <v>57635</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3283,34 +3283,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>578107</v>
+        <v>578079</v>
       </c>
       <c r="R27" t="n">
-        <v>7083998</v>
+        <v>7084109</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3345,6 +3350,11 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3357,22 +3367,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125428351</v>
+        <v>125434401</v>
       </c>
       <c r="B28" t="n">
-        <v>79565</v>
+        <v>80028</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3385,21 +3395,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3409,10 +3419,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>578034</v>
+        <v>578107</v>
       </c>
       <c r="R28" t="n">
-        <v>7084012</v>
+        <v>7083998</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3459,22 +3469,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125434403</v>
+        <v>125428351</v>
       </c>
       <c r="B29" t="n">
-        <v>80028</v>
+        <v>79565</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3487,21 +3497,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3511,10 +3521,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577951</v>
+        <v>578034</v>
       </c>
       <c r="R29" t="n">
-        <v>7084215</v>
+        <v>7084012</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3561,22 +3571,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125428364</v>
+        <v>125434403</v>
       </c>
       <c r="B30" t="n">
-        <v>91166</v>
+        <v>80028</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3589,21 +3599,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3613,10 +3623,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577941</v>
+        <v>577951</v>
       </c>
       <c r="R30" t="n">
-        <v>7084160</v>
+        <v>7084215</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3663,22 +3673,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125428366</v>
+        <v>125428364</v>
       </c>
       <c r="B31" t="n">
-        <v>57635</v>
+        <v>91166</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3691,39 +3701,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>578079</v>
+        <v>577941</v>
       </c>
       <c r="R31" t="n">
-        <v>7084109</v>
+        <v>7084160</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3756,11 +3761,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3889,10 +3889,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125434416</v>
+        <v>125428377</v>
       </c>
       <c r="B33" t="n">
-        <v>98269</v>
+        <v>91617</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3905,38 +3905,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>578014</v>
+        <v>578093</v>
       </c>
       <c r="R33" t="n">
-        <v>7084101</v>
+        <v>7084017</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3983,22 +3979,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125428377</v>
+        <v>125434416</v>
       </c>
       <c r="B34" t="n">
-        <v>91617</v>
+        <v>98269</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4011,34 +4007,38 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>578093</v>
+        <v>578014</v>
       </c>
       <c r="R34" t="n">
-        <v>7084017</v>
+        <v>7084101</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4085,22 +4085,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125428379</v>
+        <v>125428417</v>
       </c>
       <c r="B35" t="n">
-        <v>91459</v>
+        <v>98269</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4109,38 +4109,42 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578081</v>
+        <v>577924</v>
       </c>
       <c r="R35" t="n">
-        <v>7084034</v>
+        <v>7084207</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4199,7 +4203,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125428417</v>
+        <v>125428414</v>
       </c>
       <c r="B36" t="n">
         <v>98269</v>
@@ -4243,10 +4247,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577924</v>
+        <v>578131</v>
       </c>
       <c r="R36" t="n">
-        <v>7084207</v>
+        <v>7083979</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4305,10 +4309,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125428414</v>
+        <v>125428379</v>
       </c>
       <c r="B37" t="n">
-        <v>98269</v>
+        <v>91459</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4317,42 +4321,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>578131</v>
+        <v>578081</v>
       </c>
       <c r="R37" t="n">
-        <v>7083979</v>
+        <v>7084034</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4939,10 +4939,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125428408</v>
+        <v>125434404</v>
       </c>
       <c r="B43" t="n">
-        <v>98269</v>
+        <v>80028</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4951,42 +4951,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>577986</v>
+        <v>577934</v>
       </c>
       <c r="R43" t="n">
-        <v>7084157</v>
+        <v>7084194</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5033,22 +5029,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125434404</v>
+        <v>125428399</v>
       </c>
       <c r="B44" t="n">
-        <v>80028</v>
+        <v>78683</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5061,21 +5057,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5085,10 +5081,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>577934</v>
+        <v>577919</v>
       </c>
       <c r="R44" t="n">
-        <v>7084194</v>
+        <v>7084186</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5135,22 +5131,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125428399</v>
+        <v>125428408</v>
       </c>
       <c r="B45" t="n">
-        <v>78683</v>
+        <v>98269</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5159,38 +5155,42 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>577919</v>
+        <v>577986</v>
       </c>
       <c r="R45" t="n">
-        <v>7084186</v>
+        <v>7084157</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5453,10 +5453,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125428375</v>
+        <v>125428353</v>
       </c>
       <c r="B48" t="n">
-        <v>57632</v>
+        <v>79565</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5469,39 +5469,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>578148</v>
+        <v>578140</v>
       </c>
       <c r="R48" t="n">
-        <v>7083982</v>
+        <v>7083952</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5560,10 +5555,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125428353</v>
+        <v>125428419</v>
       </c>
       <c r="B49" t="n">
-        <v>79565</v>
+        <v>98269</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5572,38 +5567,42 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>578140</v>
+        <v>577910</v>
       </c>
       <c r="R49" t="n">
-        <v>7083952</v>
+        <v>7084203</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5662,10 +5661,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125428419</v>
+        <v>125428375</v>
       </c>
       <c r="B50" t="n">
-        <v>98269</v>
+        <v>57632</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5674,30 +5673,31 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5706,10 +5706,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>577910</v>
+        <v>578148</v>
       </c>
       <c r="R50" t="n">
-        <v>7084203</v>
+        <v>7083982</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>

--- a/artfynd/A 23629-2025 artfynd.xlsx
+++ b/artfynd/A 23629-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125428416</v>
+        <v>125428432</v>
       </c>
       <c r="B2" t="n">
-        <v>98269</v>
+        <v>92448</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577966</v>
+        <v>577962</v>
       </c>
       <c r="R2" t="n">
-        <v>7084168</v>
+        <v>7084183</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -781,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125428413</v>
+        <v>125428387</v>
       </c>
       <c r="B3" t="n">
-        <v>98269</v>
+        <v>80028</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,42 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578145</v>
+        <v>578115</v>
       </c>
       <c r="R3" t="n">
-        <v>7083986</v>
+        <v>7084013</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -887,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125434419</v>
+        <v>125428412</v>
       </c>
       <c r="B4" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,38 +891,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577944</v>
+        <v>578120</v>
       </c>
       <c r="R4" t="n">
-        <v>7084218</v>
+        <v>7084012</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -977,22 +973,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125428389</v>
+        <v>125428368</v>
       </c>
       <c r="B5" t="n">
-        <v>80028</v>
+        <v>80057</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1001,25 +997,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1025,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577934</v>
+        <v>577905</v>
       </c>
       <c r="R5" t="n">
-        <v>7084181</v>
+        <v>7084216</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1091,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125428376</v>
+        <v>125428389</v>
       </c>
       <c r="B6" t="n">
-        <v>57632</v>
+        <v>80028</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1107,39 +1103,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577907</v>
+        <v>577934</v>
       </c>
       <c r="R6" t="n">
-        <v>7084187</v>
+        <v>7084181</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1198,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125428378</v>
+        <v>125434403</v>
       </c>
       <c r="B7" t="n">
-        <v>91617</v>
+        <v>80028</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1210,25 +1201,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1238,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577940</v>
+        <v>577951</v>
       </c>
       <c r="R7" t="n">
-        <v>7084148</v>
+        <v>7084215</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1288,22 +1279,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125428350</v>
+        <v>125428366</v>
       </c>
       <c r="B8" t="n">
-        <v>91131</v>
+        <v>57635</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1312,38 +1303,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577904</v>
+        <v>578079</v>
       </c>
       <c r="R8" t="n">
-        <v>7084198</v>
+        <v>7084109</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1376,6 +1372,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1402,7 +1403,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125428361</v>
+        <v>125428364</v>
       </c>
       <c r="B9" t="n">
         <v>91166</v>
@@ -1442,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578081</v>
+        <v>577941</v>
       </c>
       <c r="R9" t="n">
-        <v>7084034</v>
+        <v>7084160</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1504,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125428432</v>
+        <v>125428374</v>
       </c>
       <c r="B10" t="n">
-        <v>92448</v>
+        <v>57632</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1516,38 +1517,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577962</v>
+        <v>578083</v>
       </c>
       <c r="R10" t="n">
-        <v>7084183</v>
+        <v>7084025</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1606,10 +1612,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125428425</v>
+        <v>125428399</v>
       </c>
       <c r="B11" t="n">
-        <v>91326</v>
+        <v>78683</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1618,25 +1624,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1646,10 +1652,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577972</v>
+        <v>577919</v>
       </c>
       <c r="R11" t="n">
-        <v>7084172</v>
+        <v>7084186</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1708,10 +1714,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125428404</v>
+        <v>125428376</v>
       </c>
       <c r="B12" t="n">
-        <v>78683</v>
+        <v>57632</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1724,34 +1730,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578140</v>
+        <v>577907</v>
       </c>
       <c r="R12" t="n">
-        <v>7083952</v>
+        <v>7084187</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1810,10 +1821,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125428374</v>
+        <v>125428404</v>
       </c>
       <c r="B13" t="n">
-        <v>57632</v>
+        <v>78683</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1826,39 +1837,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578083</v>
+        <v>578140</v>
       </c>
       <c r="R13" t="n">
-        <v>7084025</v>
+        <v>7083952</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1917,10 +1923,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125428397</v>
+        <v>125428377</v>
       </c>
       <c r="B14" t="n">
-        <v>78683</v>
+        <v>91617</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1929,25 +1935,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1957,10 +1963,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578084</v>
+        <v>578093</v>
       </c>
       <c r="R14" t="n">
-        <v>7084110</v>
+        <v>7084017</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2019,10 +2025,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125434405</v>
+        <v>125428362</v>
       </c>
       <c r="B15" t="n">
-        <v>80028</v>
+        <v>91166</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2035,21 +2041,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2059,10 +2065,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577902</v>
+        <v>578083</v>
       </c>
       <c r="R15" t="n">
-        <v>7084214</v>
+        <v>7084025</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2109,22 +2115,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125428411</v>
+        <v>125428428</v>
       </c>
       <c r="B16" t="n">
-        <v>98269</v>
+        <v>78947</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2133,42 +2139,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578021</v>
+        <v>578052</v>
       </c>
       <c r="R16" t="n">
-        <v>7084086</v>
+        <v>7084030</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2227,10 +2229,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125434400</v>
+        <v>125428419</v>
       </c>
       <c r="B17" t="n">
-        <v>80028</v>
+        <v>98269</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2239,38 +2241,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>578115</v>
+        <v>577910</v>
       </c>
       <c r="R17" t="n">
-        <v>7083983</v>
+        <v>7084203</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2317,22 +2323,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125428388</v>
+        <v>125434419</v>
       </c>
       <c r="B18" t="n">
-        <v>80028</v>
+        <v>78947</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2345,21 +2351,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2369,10 +2375,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>578113</v>
+        <v>577944</v>
       </c>
       <c r="R18" t="n">
-        <v>7083974</v>
+        <v>7084218</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2419,22 +2425,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125428362</v>
+        <v>125428392</v>
       </c>
       <c r="B19" t="n">
-        <v>91166</v>
+        <v>80064</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2443,25 +2449,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2471,10 +2477,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>578083</v>
+        <v>577919</v>
       </c>
       <c r="R19" t="n">
-        <v>7084025</v>
+        <v>7084203</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2533,10 +2539,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125428363</v>
+        <v>125434413</v>
       </c>
       <c r="B20" t="n">
-        <v>91166</v>
+        <v>98269</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2545,38 +2551,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>578090</v>
+        <v>578042</v>
       </c>
       <c r="R20" t="n">
-        <v>7084017</v>
+        <v>7084048</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2623,22 +2633,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125428387</v>
+        <v>125428363</v>
       </c>
       <c r="B21" t="n">
-        <v>80028</v>
+        <v>91166</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2651,21 +2661,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2675,10 +2685,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>578115</v>
+        <v>578090</v>
       </c>
       <c r="R21" t="n">
-        <v>7084013</v>
+        <v>7084017</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2737,10 +2747,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125428392</v>
+        <v>125428378</v>
       </c>
       <c r="B22" t="n">
-        <v>80064</v>
+        <v>91617</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2749,25 +2759,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6464</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2777,10 +2787,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577919</v>
+        <v>577940</v>
       </c>
       <c r="R22" t="n">
-        <v>7084203</v>
+        <v>7084148</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2839,7 +2849,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125428394</v>
+        <v>125428413</v>
       </c>
       <c r="B23" t="n">
         <v>98269</v>
@@ -2874,7 +2884,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2883,10 +2893,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>578110</v>
+        <v>578145</v>
       </c>
       <c r="R23" t="n">
-        <v>7083998</v>
+        <v>7083986</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2945,7 +2955,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125434413</v>
+        <v>125428411</v>
       </c>
       <c r="B24" t="n">
         <v>98269</v>
@@ -2980,7 +2990,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2989,10 +2999,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>578042</v>
+        <v>578021</v>
       </c>
       <c r="R24" t="n">
-        <v>7084048</v>
+        <v>7084086</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3039,22 +3049,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125428412</v>
+        <v>125428388</v>
       </c>
       <c r="B25" t="n">
-        <v>98269</v>
+        <v>80028</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3063,42 +3073,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>578120</v>
+        <v>578113</v>
       </c>
       <c r="R25" t="n">
-        <v>7084012</v>
+        <v>7083974</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3157,10 +3163,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125434417</v>
+        <v>125428350</v>
       </c>
       <c r="B26" t="n">
-        <v>56828</v>
+        <v>91131</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3169,46 +3175,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>578143</v>
+        <v>577904</v>
       </c>
       <c r="R26" t="n">
-        <v>7083969</v>
+        <v>7084198</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3255,22 +3253,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125428366</v>
+        <v>125434417</v>
       </c>
       <c r="B27" t="n">
-        <v>57635</v>
+        <v>56828</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3283,16 +3281,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3301,21 +3299,24 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>578079</v>
+        <v>578143</v>
       </c>
       <c r="R27" t="n">
-        <v>7084109</v>
+        <v>7083969</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3350,11 +3351,6 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3367,19 +3363,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125434401</v>
+        <v>125428390</v>
       </c>
       <c r="B28" t="n">
         <v>80028</v>
@@ -3419,10 +3415,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>578107</v>
+        <v>577905</v>
       </c>
       <c r="R28" t="n">
-        <v>7083998</v>
+        <v>7084216</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3469,22 +3465,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125428351</v>
+        <v>125428416</v>
       </c>
       <c r="B29" t="n">
-        <v>79565</v>
+        <v>98269</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3493,38 +3489,42 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>578034</v>
+        <v>577966</v>
       </c>
       <c r="R29" t="n">
-        <v>7084012</v>
+        <v>7084168</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3583,10 +3583,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125434403</v>
+        <v>125428408</v>
       </c>
       <c r="B30" t="n">
-        <v>80028</v>
+        <v>98269</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3595,38 +3595,42 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577951</v>
+        <v>577986</v>
       </c>
       <c r="R30" t="n">
-        <v>7084215</v>
+        <v>7084157</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3673,22 +3677,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125428364</v>
+        <v>125428394</v>
       </c>
       <c r="B31" t="n">
-        <v>91166</v>
+        <v>98269</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3697,38 +3701,42 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577941</v>
+        <v>578110</v>
       </c>
       <c r="R31" t="n">
-        <v>7084160</v>
+        <v>7083998</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3787,10 +3795,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125428428</v>
+        <v>125428375</v>
       </c>
       <c r="B32" t="n">
-        <v>78947</v>
+        <v>57632</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3803,34 +3811,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>578052</v>
+        <v>578148</v>
       </c>
       <c r="R32" t="n">
-        <v>7084030</v>
+        <v>7083982</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3889,10 +3902,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125428377</v>
+        <v>125434401</v>
       </c>
       <c r="B33" t="n">
-        <v>91617</v>
+        <v>80028</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3901,25 +3914,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3929,10 +3942,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>578093</v>
+        <v>578107</v>
       </c>
       <c r="R33" t="n">
-        <v>7084017</v>
+        <v>7083998</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3979,12 +3992,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4097,10 +4110,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125428417</v>
+        <v>125434400</v>
       </c>
       <c r="B35" t="n">
-        <v>98269</v>
+        <v>80028</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4109,42 +4122,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577924</v>
+        <v>578115</v>
       </c>
       <c r="R35" t="n">
-        <v>7084207</v>
+        <v>7083983</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4191,22 +4200,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125428414</v>
+        <v>125434404</v>
       </c>
       <c r="B36" t="n">
-        <v>98269</v>
+        <v>80028</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4215,42 +4224,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>578131</v>
+        <v>577934</v>
       </c>
       <c r="R36" t="n">
-        <v>7083979</v>
+        <v>7084194</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4297,22 +4302,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125428379</v>
+        <v>125428397</v>
       </c>
       <c r="B37" t="n">
-        <v>91459</v>
+        <v>78683</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4325,21 +4330,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4349,10 +4354,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>578081</v>
+        <v>578084</v>
       </c>
       <c r="R37" t="n">
-        <v>7084034</v>
+        <v>7084110</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4411,10 +4416,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125434414</v>
+        <v>125428367</v>
       </c>
       <c r="B38" t="n">
-        <v>98269</v>
+        <v>57635</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4423,30 +4428,31 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4455,10 +4461,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>578153</v>
+        <v>578014</v>
       </c>
       <c r="R38" t="n">
-        <v>7083956</v>
+        <v>7084091</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4493,6 +4499,11 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4505,22 +4516,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125428390</v>
+        <v>125428379</v>
       </c>
       <c r="B39" t="n">
-        <v>80028</v>
+        <v>91459</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4533,21 +4544,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4557,10 +4568,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577905</v>
+        <v>578081</v>
       </c>
       <c r="R39" t="n">
-        <v>7084216</v>
+        <v>7084034</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4619,10 +4630,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125428368</v>
+        <v>125428417</v>
       </c>
       <c r="B40" t="n">
-        <v>80057</v>
+        <v>98269</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4631,38 +4642,42 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577905</v>
+        <v>577924</v>
       </c>
       <c r="R40" t="n">
-        <v>7084216</v>
+        <v>7084207</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4721,10 +4736,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125428367</v>
+        <v>125428361</v>
       </c>
       <c r="B41" t="n">
-        <v>57635</v>
+        <v>91166</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4737,39 +4752,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>578014</v>
+        <v>578081</v>
       </c>
       <c r="R41" t="n">
-        <v>7084091</v>
+        <v>7084034</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4802,11 +4812,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4833,10 +4838,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125428415</v>
+        <v>125428425</v>
       </c>
       <c r="B42" t="n">
-        <v>98269</v>
+        <v>91326</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4849,38 +4854,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>578013</v>
+        <v>577972</v>
       </c>
       <c r="R42" t="n">
-        <v>7084064</v>
+        <v>7084172</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4939,7 +4940,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125434404</v>
+        <v>125434405</v>
       </c>
       <c r="B43" t="n">
         <v>80028</v>
@@ -4979,10 +4980,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>577934</v>
+        <v>577902</v>
       </c>
       <c r="R43" t="n">
-        <v>7084194</v>
+        <v>7084214</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5041,10 +5042,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125428399</v>
+        <v>125428430</v>
       </c>
       <c r="B44" t="n">
-        <v>78683</v>
+        <v>78947</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5057,21 +5058,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5081,10 +5082,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>577919</v>
+        <v>577976</v>
       </c>
       <c r="R44" t="n">
-        <v>7084186</v>
+        <v>7084168</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5143,7 +5144,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125428408</v>
+        <v>125428414</v>
       </c>
       <c r="B45" t="n">
         <v>98269</v>
@@ -5178,7 +5179,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5187,10 +5188,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>577986</v>
+        <v>578131</v>
       </c>
       <c r="R45" t="n">
-        <v>7084157</v>
+        <v>7083979</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5249,10 +5250,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125434402</v>
+        <v>125428353</v>
       </c>
       <c r="B46" t="n">
-        <v>80028</v>
+        <v>79565</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5265,21 +5266,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5289,10 +5290,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>578098</v>
+        <v>578140</v>
       </c>
       <c r="R46" t="n">
-        <v>7084009</v>
+        <v>7083952</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5339,22 +5340,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125428430</v>
+        <v>125428351</v>
       </c>
       <c r="B47" t="n">
-        <v>78947</v>
+        <v>79565</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5367,21 +5368,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5391,10 +5392,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>577976</v>
+        <v>578034</v>
       </c>
       <c r="R47" t="n">
-        <v>7084168</v>
+        <v>7084012</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5453,10 +5454,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125428353</v>
+        <v>125434402</v>
       </c>
       <c r="B48" t="n">
-        <v>79565</v>
+        <v>80028</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5469,21 +5470,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5493,10 +5494,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>578140</v>
+        <v>578098</v>
       </c>
       <c r="R48" t="n">
-        <v>7083952</v>
+        <v>7084009</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5543,19 +5544,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125428419</v>
+        <v>125434414</v>
       </c>
       <c r="B49" t="n">
         <v>98269</v>
@@ -5599,10 +5600,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>577910</v>
+        <v>578153</v>
       </c>
       <c r="R49" t="n">
-        <v>7084203</v>
+        <v>7083956</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5649,22 +5650,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125428375</v>
+        <v>125428415</v>
       </c>
       <c r="B50" t="n">
-        <v>57632</v>
+        <v>98269</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5673,31 +5674,30 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5706,10 +5706,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>578148</v>
+        <v>578013</v>
       </c>
       <c r="R50" t="n">
-        <v>7083982</v>
+        <v>7084064</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>

--- a/artfynd/A 23629-2025 artfynd.xlsx
+++ b/artfynd/A 23629-2025 artfynd.xlsx
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125428374</v>
+        <v>125428399</v>
       </c>
       <c r="B10" t="n">
-        <v>57632</v>
+        <v>78683</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1521,39 +1521,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578083</v>
+        <v>577919</v>
       </c>
       <c r="R10" t="n">
-        <v>7084025</v>
+        <v>7084186</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1612,10 +1607,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125428399</v>
+        <v>125428374</v>
       </c>
       <c r="B11" t="n">
-        <v>78683</v>
+        <v>57632</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1628,34 +1623,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577919</v>
+        <v>578083</v>
       </c>
       <c r="R11" t="n">
-        <v>7084186</v>
+        <v>7084025</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -3375,10 +3375,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125428390</v>
+        <v>125428416</v>
       </c>
       <c r="B28" t="n">
-        <v>80028</v>
+        <v>98269</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3387,38 +3387,42 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577905</v>
+        <v>577966</v>
       </c>
       <c r="R28" t="n">
-        <v>7084216</v>
+        <v>7084168</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3477,7 +3481,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125428416</v>
+        <v>125428408</v>
       </c>
       <c r="B29" t="n">
         <v>98269</v>
@@ -3512,7 +3516,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3521,10 +3525,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577966</v>
+        <v>577986</v>
       </c>
       <c r="R29" t="n">
-        <v>7084168</v>
+        <v>7084157</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3583,10 +3587,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125428408</v>
+        <v>125428390</v>
       </c>
       <c r="B30" t="n">
-        <v>98269</v>
+        <v>80028</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3595,42 +3599,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577986</v>
+        <v>577905</v>
       </c>
       <c r="R30" t="n">
-        <v>7084157</v>
+        <v>7084216</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3795,10 +3795,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125428375</v>
+        <v>125434401</v>
       </c>
       <c r="B32" t="n">
-        <v>57632</v>
+        <v>80028</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3811,39 +3811,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>578148</v>
+        <v>578107</v>
       </c>
       <c r="R32" t="n">
-        <v>7083982</v>
+        <v>7083998</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3890,22 +3885,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125434401</v>
+        <v>125428375</v>
       </c>
       <c r="B33" t="n">
-        <v>80028</v>
+        <v>57632</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3918,34 +3913,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>578107</v>
+        <v>578148</v>
       </c>
       <c r="R33" t="n">
-        <v>7083998</v>
+        <v>7083982</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3992,12 +3992,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>

--- a/artfynd/A 23629-2025 artfynd.xlsx
+++ b/artfynd/A 23629-2025 artfynd.xlsx
@@ -3795,10 +3795,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125434401</v>
+        <v>125428375</v>
       </c>
       <c r="B32" t="n">
-        <v>80028</v>
+        <v>57632</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3811,34 +3811,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>578107</v>
+        <v>578148</v>
       </c>
       <c r="R32" t="n">
-        <v>7083998</v>
+        <v>7083982</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3885,22 +3890,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125428375</v>
+        <v>125434401</v>
       </c>
       <c r="B33" t="n">
-        <v>57632</v>
+        <v>80028</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3913,39 +3918,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>578148</v>
+        <v>578107</v>
       </c>
       <c r="R33" t="n">
-        <v>7083982</v>
+        <v>7083998</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3992,12 +3992,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4110,10 +4110,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125434400</v>
+        <v>125428367</v>
       </c>
       <c r="B35" t="n">
-        <v>80028</v>
+        <v>57635</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4126,34 +4126,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578115</v>
+        <v>578014</v>
       </c>
       <c r="R35" t="n">
-        <v>7083983</v>
+        <v>7084091</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4188,6 +4193,11 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4200,22 +4210,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125434404</v>
+        <v>125428417</v>
       </c>
       <c r="B36" t="n">
-        <v>80028</v>
+        <v>98269</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4224,38 +4234,42 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577934</v>
+        <v>577924</v>
       </c>
       <c r="R36" t="n">
-        <v>7084194</v>
+        <v>7084207</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4302,22 +4316,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125428397</v>
+        <v>125434400</v>
       </c>
       <c r="B37" t="n">
-        <v>78683</v>
+        <v>80028</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4330,21 +4344,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4354,10 +4368,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>578084</v>
+        <v>578115</v>
       </c>
       <c r="R37" t="n">
-        <v>7084110</v>
+        <v>7083983</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4404,22 +4418,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125428367</v>
+        <v>125434404</v>
       </c>
       <c r="B38" t="n">
-        <v>57635</v>
+        <v>80028</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4432,39 +4446,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>578014</v>
+        <v>577934</v>
       </c>
       <c r="R38" t="n">
-        <v>7084091</v>
+        <v>7084194</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4499,11 +4508,6 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4516,22 +4520,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125428379</v>
+        <v>125428397</v>
       </c>
       <c r="B39" t="n">
-        <v>91459</v>
+        <v>78683</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4544,21 +4548,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4568,10 +4572,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>578081</v>
+        <v>578084</v>
       </c>
       <c r="R39" t="n">
-        <v>7084034</v>
+        <v>7084110</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4630,10 +4634,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125428417</v>
+        <v>125428379</v>
       </c>
       <c r="B40" t="n">
-        <v>98269</v>
+        <v>91459</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4642,42 +4646,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577924</v>
+        <v>578081</v>
       </c>
       <c r="R40" t="n">
-        <v>7084207</v>
+        <v>7084034</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>

--- a/artfynd/A 23629-2025 artfynd.xlsx
+++ b/artfynd/A 23629-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125428432</v>
+        <v>125428350</v>
       </c>
       <c r="B2" t="n">
-        <v>92448</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577962</v>
+        <v>577904</v>
       </c>
       <c r="R2" t="n">
-        <v>7084183</v>
+        <v>7084198</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,50 +772,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125428387</v>
+        <v>125428413</v>
       </c>
       <c r="B3" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578115</v>
+        <v>578145</v>
       </c>
       <c r="R3" t="n">
-        <v>7084013</v>
+        <v>7083986</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,15 +873,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125428412</v>
+        <v>125428417</v>
       </c>
       <c r="B4" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,7 +903,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -923,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578120</v>
+        <v>577924</v>
       </c>
       <c r="R4" t="n">
-        <v>7084012</v>
+        <v>7084207</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -985,15 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125428368</v>
+        <v>125428432</v>
       </c>
       <c r="B5" t="n">
-        <v>80057</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92502</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,21 +985,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1025,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577905</v>
+        <v>577962</v>
       </c>
       <c r="R5" t="n">
-        <v>7084216</v>
+        <v>7084183</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1087,50 +1071,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125428389</v>
+        <v>125428394</v>
       </c>
       <c r="B6" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577934</v>
+        <v>578110</v>
       </c>
       <c r="R6" t="n">
-        <v>7084181</v>
+        <v>7083998</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1189,50 +1172,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125434403</v>
+        <v>125428416</v>
       </c>
       <c r="B7" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577951</v>
+        <v>577966</v>
       </c>
       <c r="R7" t="n">
-        <v>7084215</v>
+        <v>7084168</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1279,55 +1261,49 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125428366</v>
+        <v>125428415</v>
       </c>
       <c r="B8" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1336,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578079</v>
+        <v>578013</v>
       </c>
       <c r="R8" t="n">
-        <v>7084109</v>
+        <v>7084064</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1372,11 +1348,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1403,15 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125428364</v>
+        <v>125434404</v>
       </c>
       <c r="B9" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1419,21 +1385,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577941</v>
+        <v>577934</v>
       </c>
       <c r="R9" t="n">
-        <v>7084160</v>
+        <v>7084194</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1493,49 +1459,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125428399</v>
+        <v>125428368</v>
       </c>
       <c r="B10" t="n">
-        <v>78683</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80099</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1545,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577919</v>
+        <v>577905</v>
       </c>
       <c r="R10" t="n">
-        <v>7084186</v>
+        <v>7084216</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1607,15 +1568,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125428374</v>
+        <v>125428363</v>
       </c>
       <c r="B11" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1623,39 +1579,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578083</v>
+        <v>578090</v>
       </c>
       <c r="R11" t="n">
-        <v>7084025</v>
+        <v>7084017</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1714,15 +1665,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125428376</v>
+        <v>125428399</v>
       </c>
       <c r="B12" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78725</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,39 +1676,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577907</v>
+        <v>577919</v>
       </c>
       <c r="R12" t="n">
-        <v>7084187</v>
+        <v>7084186</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1824,12 +1765,7 @@
         <v>125428404</v>
       </c>
       <c r="B13" t="n">
-        <v>78683</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78725</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1923,50 +1859,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125428377</v>
+        <v>125428376</v>
       </c>
       <c r="B14" t="n">
-        <v>91617</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578093</v>
+        <v>577907</v>
       </c>
       <c r="R14" t="n">
-        <v>7084017</v>
+        <v>7084187</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2025,50 +1961,49 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125428362</v>
+        <v>125428414</v>
       </c>
       <c r="B15" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>578083</v>
+        <v>578131</v>
       </c>
       <c r="R15" t="n">
-        <v>7084025</v>
+        <v>7083979</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2127,50 +2062,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125428428</v>
+        <v>125428411</v>
       </c>
       <c r="B16" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578052</v>
+        <v>578021</v>
       </c>
       <c r="R16" t="n">
-        <v>7084030</v>
+        <v>7084086</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2229,54 +2163,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125428419</v>
+        <v>125434400</v>
       </c>
       <c r="B17" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577910</v>
+        <v>578115</v>
       </c>
       <c r="R17" t="n">
-        <v>7084203</v>
+        <v>7083983</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2323,27 +2248,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125434419</v>
+        <v>125428430</v>
       </c>
       <c r="B18" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2375,10 +2295,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577944</v>
+        <v>577976</v>
       </c>
       <c r="R18" t="n">
-        <v>7084218</v>
+        <v>7084168</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2425,49 +2345,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125428392</v>
+        <v>125428425</v>
       </c>
       <c r="B19" t="n">
-        <v>80064</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91380</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6464</v>
+        <v>1503</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2477,10 +2392,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>577919</v>
+        <v>577972</v>
       </c>
       <c r="R19" t="n">
-        <v>7084203</v>
+        <v>7084172</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2539,54 +2454,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125434413</v>
+        <v>125428388</v>
       </c>
       <c r="B20" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>578042</v>
+        <v>578113</v>
       </c>
       <c r="R20" t="n">
-        <v>7084048</v>
+        <v>7083974</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2633,27 +2539,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125428363</v>
+        <v>125434405</v>
       </c>
       <c r="B21" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2661,21 +2562,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2685,10 +2586,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>578090</v>
+        <v>577902</v>
       </c>
       <c r="R21" t="n">
-        <v>7084017</v>
+        <v>7084214</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2735,27 +2636,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125428378</v>
+        <v>125428408</v>
       </c>
       <c r="B22" t="n">
-        <v>91617</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2763,34 +2659,38 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577940</v>
+        <v>577986</v>
       </c>
       <c r="R22" t="n">
-        <v>7084148</v>
+        <v>7084157</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2849,15 +2749,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125428413</v>
+        <v>125434413</v>
       </c>
       <c r="B23" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2893,10 +2788,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>578145</v>
+        <v>578042</v>
       </c>
       <c r="R23" t="n">
-        <v>7083986</v>
+        <v>7084048</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2943,66 +2838,57 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125428411</v>
+        <v>125434403</v>
       </c>
       <c r="B24" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>578021</v>
+        <v>577951</v>
       </c>
       <c r="R24" t="n">
-        <v>7084086</v>
+        <v>7084215</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3049,27 +2935,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125428388</v>
+        <v>125428390</v>
       </c>
       <c r="B25" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3101,10 +2982,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>578113</v>
+        <v>577905</v>
       </c>
       <c r="R25" t="n">
-        <v>7083974</v>
+        <v>7084216</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3163,37 +3044,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125428350</v>
+        <v>125428377</v>
       </c>
       <c r="B26" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91671</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3203,10 +3079,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577904</v>
+        <v>578093</v>
       </c>
       <c r="R26" t="n">
-        <v>7084198</v>
+        <v>7084017</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3265,15 +3141,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125434417</v>
+        <v>125428361</v>
       </c>
       <c r="B27" t="n">
-        <v>56828</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3281,42 +3152,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>578143</v>
+        <v>578081</v>
       </c>
       <c r="R27" t="n">
-        <v>7083969</v>
+        <v>7084034</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3363,27 +3226,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125428416</v>
+        <v>125434416</v>
       </c>
       <c r="B28" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3410,7 +3268,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3419,10 +3277,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577966</v>
+        <v>578014</v>
       </c>
       <c r="R28" t="n">
-        <v>7084168</v>
+        <v>7084101</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3469,54 +3327,50 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125428408</v>
+        <v>125428367</v>
       </c>
       <c r="B29" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3525,10 +3379,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577986</v>
+        <v>578014</v>
       </c>
       <c r="R29" t="n">
-        <v>7084157</v>
+        <v>7084091</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3561,6 +3415,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3587,15 +3446,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125428390</v>
+        <v>125428364</v>
       </c>
       <c r="B30" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3603,21 +3457,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3627,10 +3481,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577905</v>
+        <v>577941</v>
       </c>
       <c r="R30" t="n">
-        <v>7084216</v>
+        <v>7084160</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3689,51 +3543,42 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125428394</v>
+        <v>125434401</v>
       </c>
       <c r="B31" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>578110</v>
+        <v>578107</v>
       </c>
       <c r="R31" t="n">
         <v>7083998</v>
@@ -3783,27 +3628,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125428375</v>
+        <v>125428397</v>
       </c>
       <c r="B32" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78725</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3811,39 +3651,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>578148</v>
+        <v>578084</v>
       </c>
       <c r="R32" t="n">
-        <v>7083982</v>
+        <v>7084110</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3902,15 +3737,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125434401</v>
+        <v>125434402</v>
       </c>
       <c r="B33" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3942,10 +3772,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>578107</v>
+        <v>578098</v>
       </c>
       <c r="R33" t="n">
-        <v>7083998</v>
+        <v>7084009</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4004,54 +3834,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125434416</v>
+        <v>125428389</v>
       </c>
       <c r="B34" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>578014</v>
+        <v>577934</v>
       </c>
       <c r="R34" t="n">
-        <v>7084101</v>
+        <v>7084181</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4098,27 +3919,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125428367</v>
+        <v>125428374</v>
       </c>
       <c r="B35" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4126,16 +3942,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4155,10 +3971,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578014</v>
+        <v>578083</v>
       </c>
       <c r="R35" t="n">
-        <v>7084091</v>
+        <v>7084025</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4191,11 +4007,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4222,42 +4033,38 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125428417</v>
+        <v>125428366</v>
       </c>
       <c r="B36" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4266,10 +4073,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577924</v>
+        <v>578079</v>
       </c>
       <c r="R36" t="n">
-        <v>7084207</v>
+        <v>7084109</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4302,6 +4109,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4328,15 +4140,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125434400</v>
+        <v>125428387</v>
       </c>
       <c r="B37" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4371,7 +4178,7 @@
         <v>578115</v>
       </c>
       <c r="R37" t="n">
-        <v>7083983</v>
+        <v>7084013</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4418,27 +4225,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125434404</v>
+        <v>125428351</v>
       </c>
       <c r="B38" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79585</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4446,21 +4248,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4470,10 +4272,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577934</v>
+        <v>578034</v>
       </c>
       <c r="R38" t="n">
-        <v>7084194</v>
+        <v>7084012</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4520,27 +4322,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125428397</v>
+        <v>125428379</v>
       </c>
       <c r="B39" t="n">
-        <v>78683</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91513</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4548,21 +4345,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4572,10 +4369,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>578084</v>
+        <v>578081</v>
       </c>
       <c r="R39" t="n">
-        <v>7084110</v>
+        <v>7084034</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4634,15 +4431,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125428379</v>
+        <v>125428428</v>
       </c>
       <c r="B40" t="n">
-        <v>91459</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4650,21 +4442,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4674,10 +4466,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>578081</v>
+        <v>578052</v>
       </c>
       <c r="R40" t="n">
-        <v>7084034</v>
+        <v>7084030</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4736,15 +4528,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125428361</v>
+        <v>125428353</v>
       </c>
       <c r="B41" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79585</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4752,21 +4539,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4776,10 +4563,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>578081</v>
+        <v>578140</v>
       </c>
       <c r="R41" t="n">
-        <v>7084034</v>
+        <v>7083952</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4838,15 +4625,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125428425</v>
+        <v>125428412</v>
       </c>
       <c r="B42" t="n">
-        <v>91326</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4854,34 +4636,38 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>577972</v>
+        <v>578120</v>
       </c>
       <c r="R42" t="n">
-        <v>7084172</v>
+        <v>7084012</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4940,15 +4726,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125434405</v>
+        <v>125428362</v>
       </c>
       <c r="B43" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4956,21 +4737,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4980,10 +4761,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>577902</v>
+        <v>578083</v>
       </c>
       <c r="R43" t="n">
-        <v>7084214</v>
+        <v>7084025</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5030,27 +4811,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125428430</v>
+        <v>125434419</v>
       </c>
       <c r="B44" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5082,10 +4858,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>577976</v>
+        <v>577944</v>
       </c>
       <c r="R44" t="n">
-        <v>7084168</v>
+        <v>7084218</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5132,66 +4908,57 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125428414</v>
+        <v>125428392</v>
       </c>
       <c r="B45" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80106</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>578131</v>
+        <v>577919</v>
       </c>
       <c r="R45" t="n">
-        <v>7083979</v>
+        <v>7084203</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5250,15 +5017,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125428353</v>
+        <v>125428375</v>
       </c>
       <c r="B46" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5266,34 +5028,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>578140</v>
+        <v>578148</v>
       </c>
       <c r="R46" t="n">
-        <v>7083952</v>
+        <v>7083982</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5352,50 +5119,49 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125428351</v>
+        <v>125434414</v>
       </c>
       <c r="B47" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>578034</v>
+        <v>578153</v>
       </c>
       <c r="R47" t="n">
-        <v>7084012</v>
+        <v>7083956</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5442,62 +5208,61 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125434402</v>
+        <v>125428419</v>
       </c>
       <c r="B48" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>578098</v>
+        <v>577910</v>
       </c>
       <c r="R48" t="n">
-        <v>7084009</v>
+        <v>7084203</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5544,27 +5309,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125434414</v>
+        <v>125428378</v>
       </c>
       <c r="B49" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91671</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5572,38 +5332,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>578153</v>
+        <v>577940</v>
       </c>
       <c r="R49" t="n">
-        <v>7083956</v>
+        <v>7084148</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5650,66 +5406,65 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125428415</v>
+        <v>125434417</v>
       </c>
       <c r="B50" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56834</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>578013</v>
+        <v>578143</v>
       </c>
       <c r="R50" t="n">
-        <v>7084064</v>
+        <v>7083969</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5756,12 +5511,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>

--- a/artfynd/A 23629-2025 artfynd.xlsx
+++ b/artfynd/A 23629-2025 artfynd.xlsx
@@ -772,49 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125428413</v>
+        <v>125428432</v>
       </c>
       <c r="B3" t="n">
-        <v>98324</v>
+        <v>92502</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578145</v>
+        <v>577962</v>
       </c>
       <c r="R3" t="n">
-        <v>7083986</v>
+        <v>7084183</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -873,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125428417</v>
+        <v>125428413</v>
       </c>
       <c r="B4" t="n">
         <v>98324</v>
@@ -903,7 +899,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -912,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577924</v>
+        <v>578145</v>
       </c>
       <c r="R4" t="n">
-        <v>7084207</v>
+        <v>7083986</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -974,45 +970,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125428432</v>
+        <v>125428417</v>
       </c>
       <c r="B5" t="n">
-        <v>92502</v>
+        <v>98324</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577962</v>
+        <v>577924</v>
       </c>
       <c r="R5" t="n">
-        <v>7084183</v>
+        <v>7084207</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1568,45 +1568,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125428363</v>
+        <v>125428414</v>
       </c>
       <c r="B11" t="n">
-        <v>91220</v>
+        <v>98324</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578090</v>
+        <v>578131</v>
       </c>
       <c r="R11" t="n">
-        <v>7084017</v>
+        <v>7083979</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1665,45 +1669,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125428399</v>
+        <v>125428411</v>
       </c>
       <c r="B12" t="n">
-        <v>78725</v>
+        <v>98324</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577919</v>
+        <v>578021</v>
       </c>
       <c r="R12" t="n">
-        <v>7084186</v>
+        <v>7084086</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1762,10 +1770,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125428404</v>
+        <v>125428376</v>
       </c>
       <c r="B13" t="n">
-        <v>78725</v>
+        <v>57648</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1773,34 +1781,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578140</v>
+        <v>577907</v>
       </c>
       <c r="R13" t="n">
-        <v>7083952</v>
+        <v>7084187</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1859,10 +1872,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125428376</v>
+        <v>125428363</v>
       </c>
       <c r="B14" t="n">
-        <v>57648</v>
+        <v>91220</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1870,39 +1883,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577907</v>
+        <v>578090</v>
       </c>
       <c r="R14" t="n">
-        <v>7084187</v>
+        <v>7084017</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1961,49 +1969,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125428414</v>
+        <v>125428399</v>
       </c>
       <c r="B15" t="n">
-        <v>98324</v>
+        <v>78725</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>578131</v>
+        <v>577919</v>
       </c>
       <c r="R15" t="n">
-        <v>7083979</v>
+        <v>7084186</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2062,49 +2066,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125428411</v>
+        <v>125428404</v>
       </c>
       <c r="B16" t="n">
-        <v>98324</v>
+        <v>78725</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578021</v>
+        <v>578140</v>
       </c>
       <c r="R16" t="n">
-        <v>7084086</v>
+        <v>7083952</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>

--- a/artfynd/A 23629-2025 artfynd.xlsx
+++ b/artfynd/A 23629-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125428350</v>
       </c>
       <c r="B2" t="n">
-        <v>91185</v>
+        <v>91192</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,45 +772,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125428432</v>
+        <v>125428413</v>
       </c>
       <c r="B3" t="n">
-        <v>92502</v>
+        <v>98331</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577962</v>
+        <v>578145</v>
       </c>
       <c r="R3" t="n">
-        <v>7084183</v>
+        <v>7083986</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,10 +873,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125428413</v>
+        <v>125428417</v>
       </c>
       <c r="B4" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,7 +903,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -908,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578145</v>
+        <v>577924</v>
       </c>
       <c r="R4" t="n">
-        <v>7083986</v>
+        <v>7084207</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -970,49 +974,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125428417</v>
+        <v>125428432</v>
       </c>
       <c r="B5" t="n">
-        <v>98324</v>
+        <v>92509</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577924</v>
+        <v>577962</v>
       </c>
       <c r="R5" t="n">
-        <v>7084207</v>
+        <v>7084183</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1071,49 +1071,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125428394</v>
+        <v>125434404</v>
       </c>
       <c r="B6" t="n">
-        <v>98324</v>
+        <v>80070</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578110</v>
+        <v>577934</v>
       </c>
       <c r="R6" t="n">
-        <v>7083998</v>
+        <v>7084194</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1160,61 +1156,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125428416</v>
+        <v>125428368</v>
       </c>
       <c r="B7" t="n">
-        <v>98324</v>
+        <v>80099</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577966</v>
+        <v>577905</v>
       </c>
       <c r="R7" t="n">
-        <v>7084168</v>
+        <v>7084216</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1273,10 +1265,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125428415</v>
+        <v>125428394</v>
       </c>
       <c r="B8" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,7 +1295,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1312,10 +1304,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578013</v>
+        <v>578110</v>
       </c>
       <c r="R8" t="n">
-        <v>7084064</v>
+        <v>7083998</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1374,45 +1366,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125434404</v>
+        <v>125428416</v>
       </c>
       <c r="B9" t="n">
-        <v>80070</v>
+        <v>98331</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577934</v>
+        <v>577966</v>
       </c>
       <c r="R9" t="n">
-        <v>7084194</v>
+        <v>7084168</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1459,57 +1455,61 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125428368</v>
+        <v>125428415</v>
       </c>
       <c r="B10" t="n">
-        <v>80099</v>
+        <v>98331</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577905</v>
+        <v>578013</v>
       </c>
       <c r="R10" t="n">
-        <v>7084216</v>
+        <v>7084064</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1568,49 +1568,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125428414</v>
+        <v>125428363</v>
       </c>
       <c r="B11" t="n">
-        <v>98324</v>
+        <v>91227</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578131</v>
+        <v>578090</v>
       </c>
       <c r="R11" t="n">
-        <v>7083979</v>
+        <v>7084017</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1669,49 +1665,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125428411</v>
+        <v>125428399</v>
       </c>
       <c r="B12" t="n">
-        <v>98324</v>
+        <v>78725</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578021</v>
+        <v>577919</v>
       </c>
       <c r="R12" t="n">
-        <v>7084086</v>
+        <v>7084186</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1770,10 +1762,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125428376</v>
+        <v>125428404</v>
       </c>
       <c r="B13" t="n">
-        <v>57648</v>
+        <v>78725</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1781,39 +1773,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577907</v>
+        <v>578140</v>
       </c>
       <c r="R13" t="n">
-        <v>7084187</v>
+        <v>7083952</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1872,10 +1859,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125428363</v>
+        <v>125428376</v>
       </c>
       <c r="B14" t="n">
-        <v>91220</v>
+        <v>57648</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1883,34 +1870,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578090</v>
+        <v>577907</v>
       </c>
       <c r="R14" t="n">
-        <v>7084017</v>
+        <v>7084187</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1969,45 +1961,49 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125428399</v>
+        <v>125428414</v>
       </c>
       <c r="B15" t="n">
-        <v>78725</v>
+        <v>98331</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577919</v>
+        <v>578131</v>
       </c>
       <c r="R15" t="n">
-        <v>7084186</v>
+        <v>7083979</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2066,45 +2062,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125428404</v>
+        <v>125428411</v>
       </c>
       <c r="B16" t="n">
-        <v>78725</v>
+        <v>98331</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578140</v>
+        <v>578021</v>
       </c>
       <c r="R16" t="n">
-        <v>7083952</v>
+        <v>7084086</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2360,7 +2360,7 @@
         <v>125428425</v>
       </c>
       <c r="B19" t="n">
-        <v>91380</v>
+        <v>91387</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>125428408</v>
       </c>
       <c r="B22" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>125434413</v>
       </c>
       <c r="B23" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2947,32 +2947,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125428390</v>
+        <v>125428377</v>
       </c>
       <c r="B25" t="n">
-        <v>80070</v>
+        <v>91678</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577905</v>
+        <v>578093</v>
       </c>
       <c r="R25" t="n">
-        <v>7084216</v>
+        <v>7084017</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3044,32 +3044,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125428377</v>
+        <v>125428361</v>
       </c>
       <c r="B26" t="n">
-        <v>91671</v>
+        <v>91227</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>578093</v>
+        <v>578081</v>
       </c>
       <c r="R26" t="n">
-        <v>7084017</v>
+        <v>7084034</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3141,10 +3141,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125428361</v>
+        <v>125428390</v>
       </c>
       <c r="B27" t="n">
-        <v>91220</v>
+        <v>80070</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3152,21 +3152,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3176,10 +3176,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>578081</v>
+        <v>577905</v>
       </c>
       <c r="R27" t="n">
-        <v>7084034</v>
+        <v>7084216</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3241,7 +3241,7 @@
         <v>125434416</v>
       </c>
       <c r="B28" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125428367</v>
+        <v>125428364</v>
       </c>
       <c r="B29" t="n">
-        <v>57651</v>
+        <v>91227</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3350,39 +3350,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>578014</v>
+        <v>577941</v>
       </c>
       <c r="R29" t="n">
-        <v>7084091</v>
+        <v>7084160</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3415,11 +3410,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3446,10 +3436,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125428364</v>
+        <v>125428367</v>
       </c>
       <c r="B30" t="n">
-        <v>91220</v>
+        <v>57651</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3457,34 +3447,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577941</v>
+        <v>578014</v>
       </c>
       <c r="R30" t="n">
-        <v>7084160</v>
+        <v>7084091</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3517,6 +3512,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3931,10 +3931,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125428374</v>
+        <v>125428379</v>
       </c>
       <c r="B35" t="n">
-        <v>57648</v>
+        <v>91520</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3942,39 +3942,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578083</v>
+        <v>578081</v>
       </c>
       <c r="R35" t="n">
-        <v>7084025</v>
+        <v>7084034</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4334,10 +4329,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125428379</v>
+        <v>125428428</v>
       </c>
       <c r="B39" t="n">
-        <v>91513</v>
+        <v>78967</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4345,21 +4340,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4369,10 +4364,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>578081</v>
+        <v>578052</v>
       </c>
       <c r="R39" t="n">
-        <v>7084034</v>
+        <v>7084030</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4431,10 +4426,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125428428</v>
+        <v>125428374</v>
       </c>
       <c r="B40" t="n">
-        <v>78967</v>
+        <v>57648</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4442,34 +4437,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>578052</v>
+        <v>578083</v>
       </c>
       <c r="R40" t="n">
-        <v>7084030</v>
+        <v>7084025</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4528,45 +4528,49 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125428353</v>
+        <v>125428412</v>
       </c>
       <c r="B41" t="n">
-        <v>79585</v>
+        <v>98331</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>578140</v>
+        <v>578120</v>
       </c>
       <c r="R41" t="n">
-        <v>7083952</v>
+        <v>7084012</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4625,49 +4629,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125428412</v>
+        <v>125428353</v>
       </c>
       <c r="B42" t="n">
-        <v>98324</v>
+        <v>79585</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>578120</v>
+        <v>578140</v>
       </c>
       <c r="R42" t="n">
-        <v>7084012</v>
+        <v>7083952</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4729,7 +4729,7 @@
         <v>125428362</v>
       </c>
       <c r="B43" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4823,10 +4823,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125434419</v>
+        <v>125428375</v>
       </c>
       <c r="B44" t="n">
-        <v>78967</v>
+        <v>57648</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4834,34 +4834,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>577944</v>
+        <v>578148</v>
       </c>
       <c r="R44" t="n">
-        <v>7084218</v>
+        <v>7083982</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4908,44 +4913,44 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125428392</v>
+        <v>125434419</v>
       </c>
       <c r="B45" t="n">
-        <v>80106</v>
+        <v>78967</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4955,10 +4960,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>577919</v>
+        <v>577944</v>
       </c>
       <c r="R45" t="n">
-        <v>7084203</v>
+        <v>7084218</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5005,62 +5010,57 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125428375</v>
+        <v>125428392</v>
       </c>
       <c r="B46" t="n">
-        <v>57648</v>
+        <v>80106</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6464</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>578148</v>
+        <v>577919</v>
       </c>
       <c r="R46" t="n">
-        <v>7083982</v>
+        <v>7084203</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5122,7 +5122,7 @@
         <v>125434414</v>
       </c>
       <c r="B47" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>125428419</v>
       </c>
       <c r="B48" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>125428378</v>
       </c>
       <c r="B49" t="n">
-        <v>91671</v>
+        <v>91678</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 23629-2025 artfynd.xlsx
+++ b/artfynd/A 23629-2025 artfynd.xlsx
@@ -3931,10 +3931,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125428379</v>
+        <v>125428387</v>
       </c>
       <c r="B35" t="n">
-        <v>91520</v>
+        <v>80070</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3942,21 +3942,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3966,10 +3966,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578081</v>
+        <v>578115</v>
       </c>
       <c r="R35" t="n">
-        <v>7084034</v>
+        <v>7084013</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4028,10 +4028,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125428366</v>
+        <v>125428351</v>
       </c>
       <c r="B36" t="n">
-        <v>57651</v>
+        <v>79585</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4039,39 +4039,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>578079</v>
+        <v>578034</v>
       </c>
       <c r="R36" t="n">
-        <v>7084109</v>
+        <v>7084012</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4104,11 +4099,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4135,10 +4125,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125428387</v>
+        <v>125428428</v>
       </c>
       <c r="B37" t="n">
-        <v>80070</v>
+        <v>78967</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4146,21 +4136,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4170,10 +4160,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>578115</v>
+        <v>578052</v>
       </c>
       <c r="R37" t="n">
-        <v>7084013</v>
+        <v>7084030</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4232,10 +4222,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125428351</v>
+        <v>125428379</v>
       </c>
       <c r="B38" t="n">
-        <v>79585</v>
+        <v>91520</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4243,21 +4233,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4267,10 +4257,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>578034</v>
+        <v>578081</v>
       </c>
       <c r="R38" t="n">
-        <v>7084012</v>
+        <v>7084034</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4329,10 +4319,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125428428</v>
+        <v>125428374</v>
       </c>
       <c r="B39" t="n">
-        <v>78967</v>
+        <v>57648</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4340,34 +4330,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>578052</v>
+        <v>578083</v>
       </c>
       <c r="R39" t="n">
-        <v>7084030</v>
+        <v>7084025</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4426,10 +4421,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125428374</v>
+        <v>125428366</v>
       </c>
       <c r="B40" t="n">
-        <v>57648</v>
+        <v>57651</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4437,16 +4432,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4466,10 +4461,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>578083</v>
+        <v>578079</v>
       </c>
       <c r="R40" t="n">
-        <v>7084025</v>
+        <v>7084109</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4502,6 +4497,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4528,49 +4528,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125428412</v>
+        <v>125428353</v>
       </c>
       <c r="B41" t="n">
-        <v>98331</v>
+        <v>79585</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>578120</v>
+        <v>578140</v>
       </c>
       <c r="R41" t="n">
-        <v>7084012</v>
+        <v>7083952</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4629,45 +4625,49 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125428353</v>
+        <v>125428412</v>
       </c>
       <c r="B42" t="n">
-        <v>79585</v>
+        <v>98331</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>578140</v>
+        <v>578120</v>
       </c>
       <c r="R42" t="n">
-        <v>7083952</v>
+        <v>7084012</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4823,38 +4823,37 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125428375</v>
+        <v>125434414</v>
       </c>
       <c r="B44" t="n">
-        <v>57648</v>
+        <v>98331</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4863,10 +4862,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>578148</v>
+        <v>578153</v>
       </c>
       <c r="R44" t="n">
-        <v>7083982</v>
+        <v>7083956</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4913,57 +4912,61 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125434419</v>
+        <v>125428419</v>
       </c>
       <c r="B45" t="n">
-        <v>78967</v>
+        <v>98331</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>577944</v>
+        <v>577910</v>
       </c>
       <c r="R45" t="n">
-        <v>7084218</v>
+        <v>7084203</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5010,57 +5013,62 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125428392</v>
+        <v>125428375</v>
       </c>
       <c r="B46" t="n">
-        <v>80106</v>
+        <v>57648</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>577919</v>
+        <v>578148</v>
       </c>
       <c r="R46" t="n">
-        <v>7084203</v>
+        <v>7083982</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5119,49 +5127,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125434414</v>
+        <v>125434419</v>
       </c>
       <c r="B47" t="n">
-        <v>98331</v>
+        <v>78967</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>578153</v>
+        <v>577944</v>
       </c>
       <c r="R47" t="n">
-        <v>7083956</v>
+        <v>7084218</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5220,46 +5224,42 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125428419</v>
+        <v>125428392</v>
       </c>
       <c r="B48" t="n">
-        <v>98331</v>
+        <v>80106</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>577910</v>
+        <v>577919</v>
       </c>
       <c r="R48" t="n">
         <v>7084203</v>

--- a/artfynd/A 23629-2025 artfynd.xlsx
+++ b/artfynd/A 23629-2025 artfynd.xlsx
@@ -1568,10 +1568,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125428363</v>
+        <v>125428376</v>
       </c>
       <c r="B11" t="n">
-        <v>91227</v>
+        <v>57648</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1579,34 +1579,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578090</v>
+        <v>577907</v>
       </c>
       <c r="R11" t="n">
-        <v>7084017</v>
+        <v>7084187</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1665,10 +1670,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125428399</v>
+        <v>125428363</v>
       </c>
       <c r="B12" t="n">
-        <v>78725</v>
+        <v>91227</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,21 +1681,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1700,10 +1705,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577919</v>
+        <v>578090</v>
       </c>
       <c r="R12" t="n">
-        <v>7084186</v>
+        <v>7084017</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1762,7 +1767,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125428404</v>
+        <v>125428399</v>
       </c>
       <c r="B13" t="n">
         <v>78725</v>
@@ -1797,10 +1802,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578140</v>
+        <v>577919</v>
       </c>
       <c r="R13" t="n">
-        <v>7083952</v>
+        <v>7084186</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1859,10 +1864,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125428376</v>
+        <v>125428404</v>
       </c>
       <c r="B14" t="n">
-        <v>57648</v>
+        <v>78725</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1870,39 +1875,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577907</v>
+        <v>578140</v>
       </c>
       <c r="R14" t="n">
-        <v>7084187</v>
+        <v>7083952</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -3436,10 +3436,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125428367</v>
+        <v>125434401</v>
       </c>
       <c r="B30" t="n">
-        <v>57651</v>
+        <v>80070</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3447,39 +3447,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>578014</v>
+        <v>578107</v>
       </c>
       <c r="R30" t="n">
-        <v>7084091</v>
+        <v>7083998</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3514,11 +3509,6 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3531,22 +3521,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125434401</v>
+        <v>125428397</v>
       </c>
       <c r="B31" t="n">
-        <v>80070</v>
+        <v>78725</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3554,21 +3544,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3578,10 +3568,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>578107</v>
+        <v>578084</v>
       </c>
       <c r="R31" t="n">
-        <v>7083998</v>
+        <v>7084110</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3628,22 +3618,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125428397</v>
+        <v>125434402</v>
       </c>
       <c r="B32" t="n">
-        <v>78725</v>
+        <v>80070</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3651,21 +3641,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3675,10 +3665,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>578084</v>
+        <v>578098</v>
       </c>
       <c r="R32" t="n">
-        <v>7084110</v>
+        <v>7084009</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3725,19 +3715,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125434402</v>
+        <v>125428389</v>
       </c>
       <c r="B33" t="n">
         <v>80070</v>
@@ -3772,10 +3762,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>578098</v>
+        <v>577934</v>
       </c>
       <c r="R33" t="n">
-        <v>7084009</v>
+        <v>7084181</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3822,22 +3812,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125428389</v>
+        <v>125428367</v>
       </c>
       <c r="B34" t="n">
-        <v>80070</v>
+        <v>57651</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3845,34 +3835,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577934</v>
+        <v>578014</v>
       </c>
       <c r="R34" t="n">
-        <v>7084181</v>
+        <v>7084091</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3905,6 +3900,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5025,10 +5025,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125428375</v>
+        <v>125434419</v>
       </c>
       <c r="B46" t="n">
-        <v>57648</v>
+        <v>78967</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5036,39 +5036,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>578148</v>
+        <v>577944</v>
       </c>
       <c r="R46" t="n">
-        <v>7083982</v>
+        <v>7084218</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5115,44 +5110,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125434419</v>
+        <v>125428392</v>
       </c>
       <c r="B47" t="n">
-        <v>78967</v>
+        <v>80106</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5162,10 +5157,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>577944</v>
+        <v>577919</v>
       </c>
       <c r="R47" t="n">
-        <v>7084218</v>
+        <v>7084203</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5212,57 +5207,62 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125428392</v>
+        <v>125428375</v>
       </c>
       <c r="B48" t="n">
-        <v>80106</v>
+        <v>57648</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>577919</v>
+        <v>578148</v>
       </c>
       <c r="R48" t="n">
-        <v>7084203</v>
+        <v>7083982</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>

--- a/artfynd/A 23629-2025 artfynd.xlsx
+++ b/artfynd/A 23629-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125428350</v>
       </c>
       <c r="B2" t="n">
-        <v>91192</v>
+        <v>91193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,49 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125428413</v>
+        <v>125428432</v>
       </c>
       <c r="B3" t="n">
-        <v>98331</v>
+        <v>92518</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578145</v>
+        <v>577962</v>
       </c>
       <c r="R3" t="n">
-        <v>7083986</v>
+        <v>7084183</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -873,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125428417</v>
+        <v>125428413</v>
       </c>
       <c r="B4" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,7 +899,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -912,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577924</v>
+        <v>578145</v>
       </c>
       <c r="R4" t="n">
-        <v>7084207</v>
+        <v>7083986</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -974,45 +970,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125428432</v>
+        <v>125428417</v>
       </c>
       <c r="B5" t="n">
-        <v>92509</v>
+        <v>98334</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577962</v>
+        <v>577924</v>
       </c>
       <c r="R5" t="n">
-        <v>7084183</v>
+        <v>7084207</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1071,32 +1071,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125434404</v>
+        <v>125428368</v>
       </c>
       <c r="B6" t="n">
-        <v>80070</v>
+        <v>80100</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577934</v>
+        <v>577905</v>
       </c>
       <c r="R6" t="n">
-        <v>7084194</v>
+        <v>7084216</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1156,44 +1156,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125428368</v>
+        <v>125434404</v>
       </c>
       <c r="B7" t="n">
-        <v>80099</v>
+        <v>80071</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577905</v>
+        <v>577934</v>
       </c>
       <c r="R7" t="n">
-        <v>7084216</v>
+        <v>7084194</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1253,12 +1253,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1268,7 +1268,7 @@
         <v>125428394</v>
       </c>
       <c r="B8" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>125428416</v>
       </c>
       <c r="B9" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>125428415</v>
       </c>
       <c r="B10" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1568,38 +1568,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125428376</v>
+        <v>125428414</v>
       </c>
       <c r="B11" t="n">
-        <v>57648</v>
+        <v>98334</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1608,10 +1607,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577907</v>
+        <v>578131</v>
       </c>
       <c r="R11" t="n">
-        <v>7084187</v>
+        <v>7083979</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1670,45 +1669,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125428363</v>
+        <v>125428411</v>
       </c>
       <c r="B12" t="n">
-        <v>91227</v>
+        <v>98334</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578090</v>
+        <v>578021</v>
       </c>
       <c r="R12" t="n">
-        <v>7084017</v>
+        <v>7084086</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1767,10 +1770,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125428399</v>
+        <v>125428363</v>
       </c>
       <c r="B13" t="n">
-        <v>78725</v>
+        <v>91228</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1778,21 +1781,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1802,10 +1805,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577919</v>
+        <v>578090</v>
       </c>
       <c r="R13" t="n">
-        <v>7084186</v>
+        <v>7084017</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1867,7 +1870,7 @@
         <v>125428404</v>
       </c>
       <c r="B14" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1961,49 +1964,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125428414</v>
+        <v>125428399</v>
       </c>
       <c r="B15" t="n">
-        <v>98331</v>
+        <v>78726</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>578131</v>
+        <v>577919</v>
       </c>
       <c r="R15" t="n">
-        <v>7083979</v>
+        <v>7084186</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2062,37 +2061,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125428411</v>
+        <v>125428376</v>
       </c>
       <c r="B16" t="n">
-        <v>98331</v>
+        <v>57648</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578021</v>
+        <v>577907</v>
       </c>
       <c r="R16" t="n">
-        <v>7084086</v>
+        <v>7084187</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2163,10 +2163,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125434400</v>
+        <v>125428430</v>
       </c>
       <c r="B17" t="n">
-        <v>80070</v>
+        <v>78968</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2174,21 +2174,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>578115</v>
+        <v>577976</v>
       </c>
       <c r="R17" t="n">
-        <v>7083983</v>
+        <v>7084168</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2248,22 +2248,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125428430</v>
+        <v>125434400</v>
       </c>
       <c r="B18" t="n">
-        <v>78967</v>
+        <v>80071</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2271,21 +2271,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577976</v>
+        <v>578115</v>
       </c>
       <c r="R18" t="n">
-        <v>7084168</v>
+        <v>7083983</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2345,12 +2345,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2360,7 +2360,7 @@
         <v>125428425</v>
       </c>
       <c r="B19" t="n">
-        <v>91387</v>
+        <v>91389</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>125428388</v>
       </c>
       <c r="B20" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>125434405</v>
       </c>
       <c r="B21" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>125428408</v>
       </c>
       <c r="B22" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>125434413</v>
       </c>
       <c r="B23" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>125434403</v>
       </c>
       <c r="B24" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>125428377</v>
       </c>
       <c r="B25" t="n">
-        <v>91678</v>
+        <v>91682</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>125428361</v>
       </c>
       <c r="B26" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>125428390</v>
       </c>
       <c r="B27" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v>125434416</v>
       </c>
       <c r="B28" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>125428364</v>
       </c>
       <c r="B29" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3436,10 +3436,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125434401</v>
+        <v>125428389</v>
       </c>
       <c r="B30" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>578107</v>
+        <v>577934</v>
       </c>
       <c r="R30" t="n">
-        <v>7083998</v>
+        <v>7084181</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3521,22 +3521,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125428397</v>
+        <v>125434402</v>
       </c>
       <c r="B31" t="n">
-        <v>78725</v>
+        <v>80071</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3544,21 +3544,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3568,10 +3568,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>578084</v>
+        <v>578098</v>
       </c>
       <c r="R31" t="n">
-        <v>7084110</v>
+        <v>7084009</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3618,22 +3618,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125434402</v>
+        <v>125428397</v>
       </c>
       <c r="B32" t="n">
-        <v>80070</v>
+        <v>78726</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3641,21 +3641,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3665,10 +3665,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>578098</v>
+        <v>578084</v>
       </c>
       <c r="R32" t="n">
-        <v>7084009</v>
+        <v>7084110</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3715,22 +3715,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125428389</v>
+        <v>125434401</v>
       </c>
       <c r="B33" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3762,10 +3762,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>577934</v>
+        <v>578107</v>
       </c>
       <c r="R33" t="n">
-        <v>7084181</v>
+        <v>7083998</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3812,12 +3812,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -3931,10 +3931,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125428387</v>
+        <v>125428379</v>
       </c>
       <c r="B35" t="n">
-        <v>80070</v>
+        <v>91524</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3942,21 +3942,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3966,10 +3966,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578115</v>
+        <v>578081</v>
       </c>
       <c r="R35" t="n">
-        <v>7084013</v>
+        <v>7084034</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4031,7 +4031,7 @@
         <v>125428351</v>
       </c>
       <c r="B36" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>125428428</v>
       </c>
       <c r="B37" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4222,10 +4222,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125428379</v>
+        <v>125428387</v>
       </c>
       <c r="B38" t="n">
-        <v>91520</v>
+        <v>80071</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4233,21 +4233,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4257,10 +4257,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>578081</v>
+        <v>578115</v>
       </c>
       <c r="R38" t="n">
-        <v>7084034</v>
+        <v>7084013</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4528,45 +4528,49 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125428353</v>
+        <v>125428412</v>
       </c>
       <c r="B41" t="n">
-        <v>79585</v>
+        <v>98334</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>578140</v>
+        <v>578120</v>
       </c>
       <c r="R41" t="n">
-        <v>7083952</v>
+        <v>7084012</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4625,49 +4629,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125428412</v>
+        <v>125428353</v>
       </c>
       <c r="B42" t="n">
-        <v>98331</v>
+        <v>79586</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>578120</v>
+        <v>578140</v>
       </c>
       <c r="R42" t="n">
-        <v>7084012</v>
+        <v>7083952</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4729,7 +4729,7 @@
         <v>125428362</v>
       </c>
       <c r="B43" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4823,49 +4823,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125434414</v>
+        <v>125428392</v>
       </c>
       <c r="B44" t="n">
-        <v>98331</v>
+        <v>80107</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>578153</v>
+        <v>577919</v>
       </c>
       <c r="R44" t="n">
-        <v>7083956</v>
+        <v>7084203</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4912,61 +4908,57 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125428419</v>
+        <v>125434419</v>
       </c>
       <c r="B45" t="n">
-        <v>98331</v>
+        <v>78968</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>577910</v>
+        <v>577944</v>
       </c>
       <c r="R45" t="n">
-        <v>7084203</v>
+        <v>7084218</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5013,22 +5005,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125434419</v>
+        <v>125428375</v>
       </c>
       <c r="B46" t="n">
-        <v>78967</v>
+        <v>57648</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5036,34 +5028,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>577944</v>
+        <v>578148</v>
       </c>
       <c r="R46" t="n">
-        <v>7084218</v>
+        <v>7083982</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5110,57 +5107,61 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125428392</v>
+        <v>125434414</v>
       </c>
       <c r="B47" t="n">
-        <v>80106</v>
+        <v>98334</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>577919</v>
+        <v>578153</v>
       </c>
       <c r="R47" t="n">
-        <v>7084203</v>
+        <v>7083956</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5207,50 +5208,49 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125428375</v>
+        <v>125428419</v>
       </c>
       <c r="B48" t="n">
-        <v>57648</v>
+        <v>98334</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5259,10 +5259,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>578148</v>
+        <v>577910</v>
       </c>
       <c r="R48" t="n">
-        <v>7083982</v>
+        <v>7084203</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5324,7 +5324,7 @@
         <v>125428378</v>
       </c>
       <c r="B49" t="n">
-        <v>91678</v>
+        <v>91682</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 23629-2025 artfynd.xlsx
+++ b/artfynd/A 23629-2025 artfynd.xlsx
@@ -4028,10 +4028,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125428351</v>
+        <v>125428366</v>
       </c>
       <c r="B36" t="n">
-        <v>79586</v>
+        <v>57651</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4039,34 +4039,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>578034</v>
+        <v>578079</v>
       </c>
       <c r="R36" t="n">
-        <v>7084012</v>
+        <v>7084109</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4099,6 +4104,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4125,10 +4135,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125428428</v>
+        <v>125428351</v>
       </c>
       <c r="B37" t="n">
-        <v>78968</v>
+        <v>79586</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4136,21 +4146,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4160,10 +4170,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>578052</v>
+        <v>578034</v>
       </c>
       <c r="R37" t="n">
-        <v>7084030</v>
+        <v>7084012</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4222,10 +4232,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125428387</v>
+        <v>125428428</v>
       </c>
       <c r="B38" t="n">
-        <v>80071</v>
+        <v>78968</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4233,21 +4243,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4257,10 +4267,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>578115</v>
+        <v>578052</v>
       </c>
       <c r="R38" t="n">
-        <v>7084013</v>
+        <v>7084030</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4319,10 +4329,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125428374</v>
+        <v>125428387</v>
       </c>
       <c r="B39" t="n">
-        <v>57648</v>
+        <v>80071</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4330,39 +4340,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>578083</v>
+        <v>578115</v>
       </c>
       <c r="R39" t="n">
-        <v>7084025</v>
+        <v>7084013</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4421,10 +4426,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125428366</v>
+        <v>125428374</v>
       </c>
       <c r="B40" t="n">
-        <v>57651</v>
+        <v>57648</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4432,16 +4437,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4461,10 +4466,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>578079</v>
+        <v>578083</v>
       </c>
       <c r="R40" t="n">
-        <v>7084109</v>
+        <v>7084025</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4497,11 +4502,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4528,49 +4528,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125428412</v>
+        <v>125428353</v>
       </c>
       <c r="B41" t="n">
-        <v>98334</v>
+        <v>79586</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>578120</v>
+        <v>578140</v>
       </c>
       <c r="R41" t="n">
-        <v>7084012</v>
+        <v>7083952</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4629,45 +4625,49 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125428353</v>
+        <v>125428412</v>
       </c>
       <c r="B42" t="n">
-        <v>79586</v>
+        <v>98334</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>578140</v>
+        <v>578120</v>
       </c>
       <c r="R42" t="n">
-        <v>7083952</v>
+        <v>7084012</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>

--- a/artfynd/A 23629-2025 artfynd.xlsx
+++ b/artfynd/A 23629-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125428350</v>
       </c>
       <c r="B2" t="n">
-        <v>91193</v>
+        <v>91197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,45 +772,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125428432</v>
+        <v>125428413</v>
       </c>
       <c r="B3" t="n">
-        <v>92518</v>
+        <v>98338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577962</v>
+        <v>578145</v>
       </c>
       <c r="R3" t="n">
-        <v>7084183</v>
+        <v>7083986</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,10 +873,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125428413</v>
+        <v>125428417</v>
       </c>
       <c r="B4" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,7 +903,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -908,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578145</v>
+        <v>577924</v>
       </c>
       <c r="R4" t="n">
-        <v>7083986</v>
+        <v>7084207</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -970,49 +974,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125428417</v>
+        <v>125428432</v>
       </c>
       <c r="B5" t="n">
-        <v>98334</v>
+        <v>92522</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577924</v>
+        <v>577962</v>
       </c>
       <c r="R5" t="n">
-        <v>7084207</v>
+        <v>7084183</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1071,45 +1071,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125428368</v>
+        <v>125428394</v>
       </c>
       <c r="B6" t="n">
-        <v>80100</v>
+        <v>98338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577905</v>
+        <v>578110</v>
       </c>
       <c r="R6" t="n">
-        <v>7084216</v>
+        <v>7083998</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1168,45 +1172,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125434404</v>
+        <v>125428416</v>
       </c>
       <c r="B7" t="n">
-        <v>80071</v>
+        <v>98338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577934</v>
+        <v>577966</v>
       </c>
       <c r="R7" t="n">
-        <v>7084194</v>
+        <v>7084168</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1253,22 +1261,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125428394</v>
+        <v>125428415</v>
       </c>
       <c r="B8" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1295,7 +1303,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1304,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578110</v>
+        <v>578013</v>
       </c>
       <c r="R8" t="n">
-        <v>7083998</v>
+        <v>7084064</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1366,49 +1374,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125428416</v>
+        <v>125434404</v>
       </c>
       <c r="B9" t="n">
-        <v>98334</v>
+        <v>80075</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577966</v>
+        <v>577934</v>
       </c>
       <c r="R9" t="n">
-        <v>7084168</v>
+        <v>7084194</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1455,61 +1459,57 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125428415</v>
+        <v>125428368</v>
       </c>
       <c r="B10" t="n">
-        <v>98334</v>
+        <v>80104</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578013</v>
+        <v>577905</v>
       </c>
       <c r="R10" t="n">
-        <v>7084064</v>
+        <v>7084216</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1571,7 +1571,7 @@
         <v>125428414</v>
       </c>
       <c r="B11" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>125428411</v>
       </c>
       <c r="B12" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1770,10 +1770,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125428363</v>
+        <v>125428404</v>
       </c>
       <c r="B13" t="n">
-        <v>91228</v>
+        <v>78730</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1781,21 +1781,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578090</v>
+        <v>578140</v>
       </c>
       <c r="R13" t="n">
-        <v>7084017</v>
+        <v>7083952</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1867,10 +1867,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125428404</v>
+        <v>125428399</v>
       </c>
       <c r="B14" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1902,10 +1902,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578140</v>
+        <v>577919</v>
       </c>
       <c r="R14" t="n">
-        <v>7083952</v>
+        <v>7084186</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1964,10 +1964,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125428399</v>
+        <v>125428363</v>
       </c>
       <c r="B15" t="n">
-        <v>78726</v>
+        <v>91232</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1975,21 +1975,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577919</v>
+        <v>578090</v>
       </c>
       <c r="R15" t="n">
-        <v>7084186</v>
+        <v>7084017</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2166,7 +2166,7 @@
         <v>125428430</v>
       </c>
       <c r="B17" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>125434400</v>
       </c>
       <c r="B18" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>125428425</v>
       </c>
       <c r="B19" t="n">
-        <v>91389</v>
+        <v>91393</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>125428388</v>
       </c>
       <c r="B20" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2551,45 +2551,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125434405</v>
+        <v>125428408</v>
       </c>
       <c r="B21" t="n">
-        <v>80071</v>
+        <v>98338</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577902</v>
+        <v>577986</v>
       </c>
       <c r="R21" t="n">
-        <v>7084214</v>
+        <v>7084157</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2636,22 +2640,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125428408</v>
+        <v>125434413</v>
       </c>
       <c r="B22" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2678,7 +2682,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2687,10 +2691,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577986</v>
+        <v>578042</v>
       </c>
       <c r="R22" t="n">
-        <v>7084157</v>
+        <v>7084048</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2737,61 +2741,57 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125434413</v>
+        <v>125434405</v>
       </c>
       <c r="B23" t="n">
-        <v>98334</v>
+        <v>80075</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>578042</v>
+        <v>577902</v>
       </c>
       <c r="R23" t="n">
-        <v>7084048</v>
+        <v>7084214</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2853,7 +2853,7 @@
         <v>125434403</v>
       </c>
       <c r="B24" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2947,32 +2947,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125428377</v>
+        <v>125428390</v>
       </c>
       <c r="B25" t="n">
-        <v>91682</v>
+        <v>80075</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>578093</v>
+        <v>577905</v>
       </c>
       <c r="R25" t="n">
-        <v>7084017</v>
+        <v>7084216</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3044,45 +3044,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125428361</v>
+        <v>125434416</v>
       </c>
       <c r="B26" t="n">
-        <v>91228</v>
+        <v>98338</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>578081</v>
+        <v>578014</v>
       </c>
       <c r="R26" t="n">
-        <v>7084034</v>
+        <v>7084101</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3129,44 +3133,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125428390</v>
+        <v>125428377</v>
       </c>
       <c r="B27" t="n">
-        <v>80071</v>
+        <v>91686</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3176,10 +3180,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577905</v>
+        <v>578093</v>
       </c>
       <c r="R27" t="n">
-        <v>7084216</v>
+        <v>7084017</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3238,49 +3242,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125434416</v>
+        <v>125428361</v>
       </c>
       <c r="B28" t="n">
-        <v>98334</v>
+        <v>91232</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>578014</v>
+        <v>578081</v>
       </c>
       <c r="R28" t="n">
-        <v>7084101</v>
+        <v>7084034</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3327,22 +3327,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125428364</v>
+        <v>125428389</v>
       </c>
       <c r="B29" t="n">
-        <v>91228</v>
+        <v>80075</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3350,21 +3350,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3374,10 +3374,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577941</v>
+        <v>577934</v>
       </c>
       <c r="R29" t="n">
-        <v>7084160</v>
+        <v>7084181</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3436,10 +3436,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125428389</v>
+        <v>125428397</v>
       </c>
       <c r="B30" t="n">
-        <v>80071</v>
+        <v>78730</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3447,21 +3447,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577934</v>
+        <v>578084</v>
       </c>
       <c r="R30" t="n">
-        <v>7084181</v>
+        <v>7084110</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3533,10 +3533,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125434402</v>
+        <v>125428364</v>
       </c>
       <c r="B31" t="n">
-        <v>80071</v>
+        <v>91232</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3544,21 +3544,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3568,10 +3568,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>578098</v>
+        <v>577941</v>
       </c>
       <c r="R31" t="n">
-        <v>7084009</v>
+        <v>7084160</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3618,22 +3618,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125428397</v>
+        <v>125434401</v>
       </c>
       <c r="B32" t="n">
-        <v>78726</v>
+        <v>80075</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3641,21 +3641,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3665,10 +3665,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>578084</v>
+        <v>578107</v>
       </c>
       <c r="R32" t="n">
-        <v>7084110</v>
+        <v>7083998</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3715,22 +3715,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125434401</v>
+        <v>125434402</v>
       </c>
       <c r="B33" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3762,10 +3762,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>578107</v>
+        <v>578098</v>
       </c>
       <c r="R33" t="n">
-        <v>7083998</v>
+        <v>7084009</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3931,10 +3931,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125428379</v>
+        <v>125428374</v>
       </c>
       <c r="B35" t="n">
-        <v>91524</v>
+        <v>57648</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3942,34 +3942,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578081</v>
+        <v>578083</v>
       </c>
       <c r="R35" t="n">
-        <v>7084034</v>
+        <v>7084025</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4138,7 +4143,7 @@
         <v>125428351</v>
       </c>
       <c r="B37" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4235,7 +4240,7 @@
         <v>125428428</v>
       </c>
       <c r="B38" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4332,7 +4337,7 @@
         <v>125428387</v>
       </c>
       <c r="B39" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4426,10 +4431,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125428374</v>
+        <v>125428379</v>
       </c>
       <c r="B40" t="n">
-        <v>57648</v>
+        <v>91528</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4437,39 +4442,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>578083</v>
+        <v>578081</v>
       </c>
       <c r="R40" t="n">
-        <v>7084025</v>
+        <v>7084034</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4531,7 +4531,7 @@
         <v>125428353</v>
       </c>
       <c r="B41" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>125428412</v>
       </c>
       <c r="B42" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4729,7 +4729,7 @@
         <v>125428362</v>
       </c>
       <c r="B43" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4823,45 +4823,49 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125428392</v>
+        <v>125434414</v>
       </c>
       <c r="B44" t="n">
-        <v>80107</v>
+        <v>98338</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>577919</v>
+        <v>578153</v>
       </c>
       <c r="R44" t="n">
-        <v>7084203</v>
+        <v>7083956</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4908,57 +4912,61 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125434419</v>
+        <v>125428419</v>
       </c>
       <c r="B45" t="n">
-        <v>78968</v>
+        <v>98338</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>577944</v>
+        <v>577910</v>
       </c>
       <c r="R45" t="n">
-        <v>7084218</v>
+        <v>7084203</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5005,12 +5013,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5119,49 +5127,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125434414</v>
+        <v>125434419</v>
       </c>
       <c r="B47" t="n">
-        <v>98334</v>
+        <v>78972</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>578153</v>
+        <v>577944</v>
       </c>
       <c r="R47" t="n">
-        <v>7083956</v>
+        <v>7084218</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5220,46 +5224,42 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125428419</v>
+        <v>125428392</v>
       </c>
       <c r="B48" t="n">
-        <v>98334</v>
+        <v>80111</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>577910</v>
+        <v>577919</v>
       </c>
       <c r="R48" t="n">
         <v>7084203</v>
@@ -5324,7 +5324,7 @@
         <v>125428378</v>
       </c>
       <c r="B49" t="n">
-        <v>91682</v>
+        <v>91686</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 23629-2025 artfynd.xlsx
+++ b/artfynd/A 23629-2025 artfynd.xlsx
@@ -1964,10 +1964,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125428363</v>
+        <v>125428376</v>
       </c>
       <c r="B15" t="n">
-        <v>91232</v>
+        <v>57648</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1975,34 +1975,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>578090</v>
+        <v>577907</v>
       </c>
       <c r="R15" t="n">
-        <v>7084017</v>
+        <v>7084187</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2061,10 +2066,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125428376</v>
+        <v>125428363</v>
       </c>
       <c r="B16" t="n">
-        <v>57648</v>
+        <v>91232</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2072,39 +2077,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577907</v>
+        <v>578090</v>
       </c>
       <c r="R16" t="n">
-        <v>7084187</v>
+        <v>7084017</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2947,45 +2947,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125428390</v>
+        <v>125434416</v>
       </c>
       <c r="B25" t="n">
-        <v>80075</v>
+        <v>98338</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577905</v>
+        <v>578014</v>
       </c>
       <c r="R25" t="n">
-        <v>7084216</v>
+        <v>7084101</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3032,22 +3036,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125434416</v>
+        <v>125428377</v>
       </c>
       <c r="B26" t="n">
-        <v>98338</v>
+        <v>91686</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3055,38 +3059,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>578014</v>
+        <v>578093</v>
       </c>
       <c r="R26" t="n">
-        <v>7084101</v>
+        <v>7084017</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3133,44 +3133,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125428377</v>
+        <v>125428361</v>
       </c>
       <c r="B27" t="n">
-        <v>91686</v>
+        <v>91232</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>578093</v>
+        <v>578081</v>
       </c>
       <c r="R27" t="n">
-        <v>7084017</v>
+        <v>7084034</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3242,10 +3242,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125428361</v>
+        <v>125428390</v>
       </c>
       <c r="B28" t="n">
-        <v>91232</v>
+        <v>80075</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3253,21 +3253,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3277,10 +3277,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>578081</v>
+        <v>577905</v>
       </c>
       <c r="R28" t="n">
-        <v>7084034</v>
+        <v>7084216</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3630,10 +3630,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125434401</v>
+        <v>125428367</v>
       </c>
       <c r="B32" t="n">
-        <v>80075</v>
+        <v>57651</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3641,34 +3641,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>578107</v>
+        <v>578014</v>
       </c>
       <c r="R32" t="n">
-        <v>7083998</v>
+        <v>7084091</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3703,6 +3708,11 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -3715,19 +3725,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125434402</v>
+        <v>125434401</v>
       </c>
       <c r="B33" t="n">
         <v>80075</v>
@@ -3762,10 +3772,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>578098</v>
+        <v>578107</v>
       </c>
       <c r="R33" t="n">
-        <v>7084009</v>
+        <v>7083998</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3824,10 +3834,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125428367</v>
+        <v>125434402</v>
       </c>
       <c r="B34" t="n">
-        <v>57651</v>
+        <v>80075</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3835,39 +3845,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>578014</v>
+        <v>578098</v>
       </c>
       <c r="R34" t="n">
-        <v>7084091</v>
+        <v>7084009</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3902,11 +3907,6 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -3919,12 +3919,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>

--- a/artfynd/A 23629-2025 artfynd.xlsx
+++ b/artfynd/A 23629-2025 artfynd.xlsx
@@ -772,49 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125428413</v>
+        <v>125428432</v>
       </c>
       <c r="B3" t="n">
-        <v>98338</v>
+        <v>92522</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578145</v>
+        <v>577962</v>
       </c>
       <c r="R3" t="n">
-        <v>7083986</v>
+        <v>7084183</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -876,7 +872,7 @@
         <v>125428417</v>
       </c>
       <c r="B4" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,45 +970,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125428432</v>
+        <v>125428413</v>
       </c>
       <c r="B5" t="n">
-        <v>92522</v>
+        <v>98339</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577962</v>
+        <v>578145</v>
       </c>
       <c r="R5" t="n">
-        <v>7084183</v>
+        <v>7083986</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1071,49 +1071,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125428394</v>
+        <v>125434404</v>
       </c>
       <c r="B6" t="n">
-        <v>98338</v>
+        <v>80075</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578110</v>
+        <v>577934</v>
       </c>
       <c r="R6" t="n">
-        <v>7083998</v>
+        <v>7084194</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1160,61 +1156,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125428416</v>
+        <v>125428368</v>
       </c>
       <c r="B7" t="n">
-        <v>98338</v>
+        <v>80104</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577966</v>
+        <v>577905</v>
       </c>
       <c r="R7" t="n">
-        <v>7084168</v>
+        <v>7084216</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1273,10 +1265,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125428415</v>
+        <v>125428416</v>
       </c>
       <c r="B8" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,7 +1295,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1312,10 +1304,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578013</v>
+        <v>577966</v>
       </c>
       <c r="R8" t="n">
-        <v>7084064</v>
+        <v>7084168</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1374,45 +1366,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125434404</v>
+        <v>125428415</v>
       </c>
       <c r="B9" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577934</v>
+        <v>578013</v>
       </c>
       <c r="R9" t="n">
-        <v>7084194</v>
+        <v>7084064</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1459,57 +1455,61 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125428368</v>
+        <v>125428394</v>
       </c>
       <c r="B10" t="n">
-        <v>80104</v>
+        <v>98339</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577905</v>
+        <v>578110</v>
       </c>
       <c r="R10" t="n">
-        <v>7084216</v>
+        <v>7083998</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1568,49 +1568,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125428414</v>
+        <v>125428399</v>
       </c>
       <c r="B11" t="n">
-        <v>98338</v>
+        <v>78730</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578131</v>
+        <v>577919</v>
       </c>
       <c r="R11" t="n">
-        <v>7083979</v>
+        <v>7084186</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1669,49 +1665,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125428411</v>
+        <v>125428404</v>
       </c>
       <c r="B12" t="n">
-        <v>98338</v>
+        <v>78730</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578021</v>
+        <v>578140</v>
       </c>
       <c r="R12" t="n">
-        <v>7084086</v>
+        <v>7083952</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1770,10 +1762,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125428404</v>
+        <v>125428376</v>
       </c>
       <c r="B13" t="n">
-        <v>78730</v>
+        <v>57648</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1781,34 +1773,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578140</v>
+        <v>577907</v>
       </c>
       <c r="R13" t="n">
-        <v>7083952</v>
+        <v>7084187</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1867,45 +1864,49 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125428399</v>
+        <v>125428411</v>
       </c>
       <c r="B14" t="n">
-        <v>78730</v>
+        <v>98339</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577919</v>
+        <v>578021</v>
       </c>
       <c r="R14" t="n">
-        <v>7084186</v>
+        <v>7084086</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1964,10 +1965,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125428376</v>
+        <v>125428363</v>
       </c>
       <c r="B15" t="n">
-        <v>57648</v>
+        <v>91232</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1975,39 +1976,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577907</v>
+        <v>578090</v>
       </c>
       <c r="R15" t="n">
-        <v>7084187</v>
+        <v>7084017</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2066,45 +2062,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125428363</v>
+        <v>125428414</v>
       </c>
       <c r="B16" t="n">
-        <v>91232</v>
+        <v>98339</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578090</v>
+        <v>578131</v>
       </c>
       <c r="R16" t="n">
-        <v>7084017</v>
+        <v>7083979</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2163,10 +2163,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125428430</v>
+        <v>125434400</v>
       </c>
       <c r="B17" t="n">
-        <v>78972</v>
+        <v>80075</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2174,21 +2174,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577976</v>
+        <v>578115</v>
       </c>
       <c r="R17" t="n">
-        <v>7084168</v>
+        <v>7083983</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2248,22 +2248,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125434400</v>
+        <v>125428430</v>
       </c>
       <c r="B18" t="n">
-        <v>80075</v>
+        <v>78972</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2271,21 +2271,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>578115</v>
+        <v>577976</v>
       </c>
       <c r="R18" t="n">
-        <v>7083983</v>
+        <v>7084168</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2345,12 +2345,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2554,7 +2554,7 @@
         <v>125428408</v>
       </c>
       <c r="B21" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>125434413</v>
       </c>
       <c r="B22" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>125434416</v>
       </c>
       <c r="B25" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125428389</v>
+        <v>125428364</v>
       </c>
       <c r="B29" t="n">
-        <v>80075</v>
+        <v>91232</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3350,21 +3350,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3374,10 +3374,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577934</v>
+        <v>577941</v>
       </c>
       <c r="R29" t="n">
-        <v>7084181</v>
+        <v>7084160</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3436,10 +3436,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125428397</v>
+        <v>125428367</v>
       </c>
       <c r="B30" t="n">
-        <v>78730</v>
+        <v>57651</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3447,34 +3447,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>578084</v>
+        <v>578014</v>
       </c>
       <c r="R30" t="n">
-        <v>7084110</v>
+        <v>7084091</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3507,6 +3512,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3533,10 +3543,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125428364</v>
+        <v>125434401</v>
       </c>
       <c r="B31" t="n">
-        <v>91232</v>
+        <v>80075</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3544,21 +3554,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3568,10 +3578,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577941</v>
+        <v>578107</v>
       </c>
       <c r="R31" t="n">
-        <v>7084160</v>
+        <v>7083998</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3618,22 +3628,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125428367</v>
+        <v>125428397</v>
       </c>
       <c r="B32" t="n">
-        <v>57651</v>
+        <v>78730</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3641,39 +3651,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>578014</v>
+        <v>578084</v>
       </c>
       <c r="R32" t="n">
-        <v>7084091</v>
+        <v>7084110</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3706,11 +3711,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3737,7 +3737,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125434401</v>
+        <v>125434402</v>
       </c>
       <c r="B33" t="n">
         <v>80075</v>
@@ -3772,10 +3772,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>578107</v>
+        <v>578098</v>
       </c>
       <c r="R33" t="n">
-        <v>7083998</v>
+        <v>7084009</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3834,7 +3834,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125434402</v>
+        <v>125428389</v>
       </c>
       <c r="B34" t="n">
         <v>80075</v>
@@ -3869,10 +3869,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>578098</v>
+        <v>577934</v>
       </c>
       <c r="R34" t="n">
-        <v>7084009</v>
+        <v>7084181</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3919,22 +3919,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125428374</v>
+        <v>125428379</v>
       </c>
       <c r="B35" t="n">
-        <v>57648</v>
+        <v>91528</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3942,39 +3942,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578083</v>
+        <v>578081</v>
       </c>
       <c r="R35" t="n">
-        <v>7084025</v>
+        <v>7084034</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4033,10 +4028,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125428366</v>
+        <v>125428374</v>
       </c>
       <c r="B36" t="n">
-        <v>57651</v>
+        <v>57648</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4044,16 +4039,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4073,10 +4068,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>578079</v>
+        <v>578083</v>
       </c>
       <c r="R36" t="n">
-        <v>7084109</v>
+        <v>7084025</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4109,11 +4104,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4140,10 +4130,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125428351</v>
+        <v>125428366</v>
       </c>
       <c r="B37" t="n">
-        <v>79590</v>
+        <v>57651</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4151,34 +4141,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>578034</v>
+        <v>578079</v>
       </c>
       <c r="R37" t="n">
-        <v>7084012</v>
+        <v>7084109</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4211,6 +4206,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4237,10 +4237,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125428428</v>
+        <v>125428387</v>
       </c>
       <c r="B38" t="n">
-        <v>78972</v>
+        <v>80075</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4248,21 +4248,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4272,10 +4272,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>578052</v>
+        <v>578115</v>
       </c>
       <c r="R38" t="n">
-        <v>7084030</v>
+        <v>7084013</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4334,10 +4334,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125428387</v>
+        <v>125428351</v>
       </c>
       <c r="B39" t="n">
-        <v>80075</v>
+        <v>79590</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4345,21 +4345,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4369,10 +4369,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>578115</v>
+        <v>578034</v>
       </c>
       <c r="R39" t="n">
-        <v>7084013</v>
+        <v>7084012</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4431,10 +4431,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125428379</v>
+        <v>125428428</v>
       </c>
       <c r="B40" t="n">
-        <v>91528</v>
+        <v>78972</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4442,21 +4442,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4466,10 +4466,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>578081</v>
+        <v>578052</v>
       </c>
       <c r="R40" t="n">
-        <v>7084034</v>
+        <v>7084030</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4528,45 +4528,49 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125428353</v>
+        <v>125428412</v>
       </c>
       <c r="B41" t="n">
-        <v>79590</v>
+        <v>98339</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>578140</v>
+        <v>578120</v>
       </c>
       <c r="R41" t="n">
-        <v>7083952</v>
+        <v>7084012</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4625,49 +4629,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125428412</v>
+        <v>125428353</v>
       </c>
       <c r="B42" t="n">
-        <v>98338</v>
+        <v>79590</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>578120</v>
+        <v>578140</v>
       </c>
       <c r="R42" t="n">
-        <v>7084012</v>
+        <v>7083952</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4823,49 +4823,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125434414</v>
+        <v>125434419</v>
       </c>
       <c r="B44" t="n">
-        <v>98338</v>
+        <v>78972</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>578153</v>
+        <v>577944</v>
       </c>
       <c r="R44" t="n">
-        <v>7083956</v>
+        <v>7084218</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4924,46 +4920,42 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125428419</v>
+        <v>125428392</v>
       </c>
       <c r="B45" t="n">
-        <v>98338</v>
+        <v>80111</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>577910</v>
+        <v>577919</v>
       </c>
       <c r="R45" t="n">
         <v>7084203</v>
@@ -5127,45 +5119,49 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125434419</v>
+        <v>125434414</v>
       </c>
       <c r="B47" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>577944</v>
+        <v>578153</v>
       </c>
       <c r="R47" t="n">
-        <v>7084218</v>
+        <v>7083956</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5224,42 +5220,46 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125428392</v>
+        <v>125428419</v>
       </c>
       <c r="B48" t="n">
-        <v>80111</v>
+        <v>98339</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>577919</v>
+        <v>577910</v>
       </c>
       <c r="R48" t="n">
         <v>7084203</v>

--- a/artfynd/A 23629-2025 artfynd.xlsx
+++ b/artfynd/A 23629-2025 artfynd.xlsx
@@ -2947,10 +2947,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125434416</v>
+        <v>125428377</v>
       </c>
       <c r="B25" t="n">
-        <v>98339</v>
+        <v>91686</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2958,38 +2958,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>578014</v>
+        <v>578093</v>
       </c>
       <c r="R25" t="n">
-        <v>7084101</v>
+        <v>7084017</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3036,44 +3032,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125428377</v>
+        <v>125428361</v>
       </c>
       <c r="B26" t="n">
-        <v>91686</v>
+        <v>91232</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3083,10 +3079,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>578093</v>
+        <v>578081</v>
       </c>
       <c r="R26" t="n">
-        <v>7084017</v>
+        <v>7084034</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3145,10 +3141,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125428361</v>
+        <v>125428390</v>
       </c>
       <c r="B27" t="n">
-        <v>91232</v>
+        <v>80075</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3156,21 +3152,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3180,10 +3176,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>578081</v>
+        <v>577905</v>
       </c>
       <c r="R27" t="n">
-        <v>7084034</v>
+        <v>7084216</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3242,45 +3238,49 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125428390</v>
+        <v>125434416</v>
       </c>
       <c r="B28" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577905</v>
+        <v>578014</v>
       </c>
       <c r="R28" t="n">
-        <v>7084216</v>
+        <v>7084101</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3327,12 +3327,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3931,10 +3931,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125428379</v>
+        <v>125428387</v>
       </c>
       <c r="B35" t="n">
-        <v>91528</v>
+        <v>80075</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3942,21 +3942,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3966,10 +3966,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578081</v>
+        <v>578115</v>
       </c>
       <c r="R35" t="n">
-        <v>7084034</v>
+        <v>7084013</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4028,10 +4028,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125428374</v>
+        <v>125428351</v>
       </c>
       <c r="B36" t="n">
-        <v>57648</v>
+        <v>79590</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4039,39 +4039,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>578083</v>
+        <v>578034</v>
       </c>
       <c r="R36" t="n">
-        <v>7084025</v>
+        <v>7084012</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4130,10 +4125,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125428366</v>
+        <v>125428428</v>
       </c>
       <c r="B37" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4141,39 +4136,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>578079</v>
+        <v>578052</v>
       </c>
       <c r="R37" t="n">
-        <v>7084109</v>
+        <v>7084030</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4206,11 +4196,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4237,10 +4222,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125428387</v>
+        <v>125428366</v>
       </c>
       <c r="B38" t="n">
-        <v>80075</v>
+        <v>57651</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4248,34 +4233,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>578115</v>
+        <v>578079</v>
       </c>
       <c r="R38" t="n">
-        <v>7084013</v>
+        <v>7084109</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4308,6 +4298,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4334,10 +4329,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125428351</v>
+        <v>125428379</v>
       </c>
       <c r="B39" t="n">
-        <v>79590</v>
+        <v>91528</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4345,21 +4340,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4369,10 +4364,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>578034</v>
+        <v>578081</v>
       </c>
       <c r="R39" t="n">
-        <v>7084012</v>
+        <v>7084034</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4431,10 +4426,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125428428</v>
+        <v>125428374</v>
       </c>
       <c r="B40" t="n">
-        <v>78972</v>
+        <v>57648</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4442,34 +4437,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>578052</v>
+        <v>578083</v>
       </c>
       <c r="R40" t="n">
-        <v>7084030</v>
+        <v>7084025</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>

--- a/artfynd/A 23629-2025 artfynd.xlsx
+++ b/artfynd/A 23629-2025 artfynd.xlsx
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125428417</v>
+        <v>125428413</v>
       </c>
       <c r="B4" t="n">
         <v>98339</v>
@@ -899,7 +899,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -908,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577924</v>
+        <v>578145</v>
       </c>
       <c r="R4" t="n">
-        <v>7084207</v>
+        <v>7083986</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -970,7 +970,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125428413</v>
+        <v>125428417</v>
       </c>
       <c r="B5" t="n">
         <v>98339</v>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578145</v>
+        <v>577924</v>
       </c>
       <c r="R5" t="n">
-        <v>7083986</v>
+        <v>7084207</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1762,10 +1762,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125428376</v>
+        <v>125428363</v>
       </c>
       <c r="B13" t="n">
-        <v>57648</v>
+        <v>91232</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1773,39 +1773,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577907</v>
+        <v>578090</v>
       </c>
       <c r="R13" t="n">
-        <v>7084187</v>
+        <v>7084017</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1864,37 +1859,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125428411</v>
+        <v>125428376</v>
       </c>
       <c r="B14" t="n">
-        <v>98339</v>
+        <v>57648</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1903,10 +1899,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578021</v>
+        <v>577907</v>
       </c>
       <c r="R14" t="n">
-        <v>7084086</v>
+        <v>7084187</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1965,45 +1961,49 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125428363</v>
+        <v>125428414</v>
       </c>
       <c r="B15" t="n">
-        <v>91232</v>
+        <v>98339</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>578090</v>
+        <v>578131</v>
       </c>
       <c r="R15" t="n">
-        <v>7084017</v>
+        <v>7083979</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2062,7 +2062,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125428414</v>
+        <v>125428411</v>
       </c>
       <c r="B16" t="n">
         <v>98339</v>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578131</v>
+        <v>578021</v>
       </c>
       <c r="R16" t="n">
-        <v>7083979</v>
+        <v>7084086</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -3931,10 +3931,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125428387</v>
+        <v>125428379</v>
       </c>
       <c r="B35" t="n">
-        <v>80075</v>
+        <v>91528</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3942,21 +3942,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3966,10 +3966,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578115</v>
+        <v>578081</v>
       </c>
       <c r="R35" t="n">
-        <v>7084013</v>
+        <v>7084034</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4028,10 +4028,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125428351</v>
+        <v>125428374</v>
       </c>
       <c r="B36" t="n">
-        <v>79590</v>
+        <v>57648</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4039,34 +4039,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>578034</v>
+        <v>578083</v>
       </c>
       <c r="R36" t="n">
-        <v>7084012</v>
+        <v>7084025</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4125,10 +4130,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125428428</v>
+        <v>125428366</v>
       </c>
       <c r="B37" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4136,34 +4141,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>578052</v>
+        <v>578079</v>
       </c>
       <c r="R37" t="n">
-        <v>7084030</v>
+        <v>7084109</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4196,6 +4206,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4222,10 +4237,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125428366</v>
+        <v>125428387</v>
       </c>
       <c r="B38" t="n">
-        <v>57651</v>
+        <v>80075</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4233,39 +4248,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>578079</v>
+        <v>578115</v>
       </c>
       <c r="R38" t="n">
-        <v>7084109</v>
+        <v>7084013</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4298,11 +4308,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4329,10 +4334,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125428379</v>
+        <v>125428351</v>
       </c>
       <c r="B39" t="n">
-        <v>91528</v>
+        <v>79590</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4340,21 +4345,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4364,10 +4369,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>578081</v>
+        <v>578034</v>
       </c>
       <c r="R39" t="n">
-        <v>7084034</v>
+        <v>7084012</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4426,10 +4431,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125428374</v>
+        <v>125428428</v>
       </c>
       <c r="B40" t="n">
-        <v>57648</v>
+        <v>78972</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4437,39 +4442,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>578083</v>
+        <v>578052</v>
       </c>
       <c r="R40" t="n">
-        <v>7084025</v>
+        <v>7084030</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
